--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,27 @@
         <v>63.08</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="E54" t="n">
+        <v>66.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>42.6</v>
       </c>
       <c r="D2" t="n">
-        <v>34.2</v>
+        <v>42.5</v>
       </c>
       <c r="E2" t="n">
-        <v>50.44</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.6</v>
+        <v>39.8</v>
       </c>
       <c r="D3" t="n">
-        <v>42.5</v>
+        <v>38.1</v>
       </c>
       <c r="E3" t="n">
-        <v>52.8</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -497,19 +497,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39.8</v>
+        <v>47.8</v>
       </c>
       <c r="D4" t="n">
-        <v>38.1</v>
+        <v>46.4</v>
       </c>
       <c r="E4" t="n">
-        <v>51.24</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47.8</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>46.4</v>
+        <v>34.4</v>
       </c>
       <c r="E5" t="n">
-        <v>56.04</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,19 +539,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>30.4</v>
       </c>
       <c r="D6" t="n">
-        <v>34.4</v>
+        <v>24.8</v>
       </c>
       <c r="E6" t="n">
-        <v>49.56</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -560,19 +560,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.4</v>
+        <v>38.2</v>
       </c>
       <c r="D7" t="n">
-        <v>24.8</v>
+        <v>33.5</v>
       </c>
       <c r="E7" t="n">
-        <v>44.52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38.2</v>
+        <v>40.2</v>
       </c>
       <c r="D8" t="n">
-        <v>33.5</v>
+        <v>37.5</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40.2</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>37.5</v>
+        <v>25.2</v>
       </c>
       <c r="E9" t="n">
-        <v>49.68</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>15.6</v>
       </c>
       <c r="D10" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="E10" t="n">
-        <v>44.52</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -644,19 +644,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="D11" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="E11" t="n">
-        <v>38.08</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -665,19 +665,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.2</v>
+        <v>2.4</v>
       </c>
       <c r="D12" t="n">
-        <v>20.8</v>
+        <v>11.6</v>
       </c>
       <c r="E12" t="n">
-        <v>37.52</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -686,40 +686,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="D13" t="n">
-        <v>11.6</v>
+        <v>5.3</v>
       </c>
       <c r="E13" t="n">
-        <v>36.44</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-2.6</v>
+        <v>15.8</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3</v>
+        <v>33.45</v>
       </c>
       <c r="E14" t="n">
-        <v>29.8</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -728,19 +728,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>33.45</v>
+        <v>28.95</v>
       </c>
       <c r="E15" t="n">
-        <v>36.83</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="D16" t="n">
-        <v>28.95</v>
+        <v>25.85</v>
       </c>
       <c r="E16" t="n">
-        <v>33.37</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="E17" t="n">
-        <v>30.74</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D18" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E18" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E18" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D19" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E19" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D20" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E20" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -854,19 +854,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D21" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E21" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -875,19 +875,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D22" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E22" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -896,19 +896,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D23" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E23" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D24" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E24" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D25" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E25" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D26" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E26" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D27" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E27" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1001,19 +1001,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D28" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E28" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1022,19 +1022,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D29" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E29" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D30" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E30" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1064,19 +1064,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1085,19 +1085,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D32" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E32" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1106,40 +1106,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E33" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D34" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E34" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1148,19 +1148,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D35" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E35" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1169,19 +1169,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D36" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E36" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1190,19 +1190,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D37" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E37" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1211,19 +1211,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D38" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E38" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D39" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E39" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D40" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E40" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D41" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E41" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1295,19 +1295,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D42" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E42" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D43" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E43" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1337,19 +1337,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D44" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E44" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1358,19 +1358,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D45" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E45" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1379,19 +1379,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D46" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E46" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1400,19 +1400,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D47" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E47" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1421,19 +1421,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D48" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E48" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1442,19 +1442,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D49" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E49" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1463,40 +1463,40 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D50" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E50" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D51" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E51" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1505,19 +1505,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D53" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E53" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>42.6</v>
       </c>
       <c r="D2" t="n">
-        <v>34.2</v>
+        <v>42.5</v>
       </c>
       <c r="E2" t="n">
-        <v>50.44</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.6</v>
+        <v>39.8</v>
       </c>
       <c r="D3" t="n">
-        <v>42.5</v>
+        <v>38.1</v>
       </c>
       <c r="E3" t="n">
-        <v>52.8</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39.8</v>
+        <v>47.8</v>
       </c>
       <c r="D4" t="n">
-        <v>38.1</v>
+        <v>46.4</v>
       </c>
       <c r="E4" t="n">
-        <v>51.24</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47.8</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>46.4</v>
+        <v>34.4</v>
       </c>
       <c r="E5" t="n">
-        <v>56.04</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>30.4</v>
       </c>
       <c r="D6" t="n">
-        <v>34.4</v>
+        <v>24.8</v>
       </c>
       <c r="E6" t="n">
-        <v>49.56</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.4</v>
+        <v>38.2</v>
       </c>
       <c r="D7" t="n">
-        <v>24.8</v>
+        <v>33.5</v>
       </c>
       <c r="E7" t="n">
-        <v>44.52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38.2</v>
+        <v>40.2</v>
       </c>
       <c r="D8" t="n">
-        <v>33.5</v>
+        <v>37.5</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40.2</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>37.5</v>
+        <v>25.2</v>
       </c>
       <c r="E9" t="n">
-        <v>49.68</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>15.6</v>
       </c>
       <c r="D10" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="E10" t="n">
-        <v>44.52</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="D11" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="E11" t="n">
-        <v>38.08</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.2</v>
+        <v>2.4</v>
       </c>
       <c r="D12" t="n">
-        <v>20.8</v>
+        <v>11.6</v>
       </c>
       <c r="E12" t="n">
-        <v>37.52</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,40 +698,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="D13" t="n">
-        <v>11.6</v>
+        <v>5.3</v>
       </c>
       <c r="E13" t="n">
-        <v>36.44</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-2.6</v>
+        <v>15.8</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3</v>
+        <v>33.45</v>
       </c>
       <c r="E14" t="n">
-        <v>29.8</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>33.45</v>
+        <v>28.95</v>
       </c>
       <c r="E15" t="n">
-        <v>36.83</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="D16" t="n">
-        <v>28.95</v>
+        <v>25.85</v>
       </c>
       <c r="E16" t="n">
-        <v>33.37</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="E17" t="n">
-        <v>30.74</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D18" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E18" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E18" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D19" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E19" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D20" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E20" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D21" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E21" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D22" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E22" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D23" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E23" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D24" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E24" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D25" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E25" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D26" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E26" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D27" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E27" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D28" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E28" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D29" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E29" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D30" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E30" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D32" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E32" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,40 +1118,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E33" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D34" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E34" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D35" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E35" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D36" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E36" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D37" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E37" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D38" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E38" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D39" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E39" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D40" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E40" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D41" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E41" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D42" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E42" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D43" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E43" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D44" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E44" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D45" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E45" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D46" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E46" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D47" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E47" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D48" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E48" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D49" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E49" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,40 +1475,40 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D50" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E50" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D51" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E51" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,33 +1538,12 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D53" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E53" t="n">
-        <v>63.08</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>IC2604</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="D54" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="E54" t="n">
         <v>66.12</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,27 @@
         <v>66.12</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>66.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,6 +1568,27 @@
         <v>66.2</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E55" t="n">
+        <v>63.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42.6</v>
+        <v>47.8</v>
       </c>
       <c r="D2" t="n">
-        <v>42.5</v>
+        <v>46.4</v>
       </c>
       <c r="E2" t="n">
-        <v>52.8</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>38.1</v>
+        <v>34.4</v>
       </c>
       <c r="E3" t="n">
-        <v>51.24</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47.8</v>
+        <v>30.4</v>
       </c>
       <c r="D4" t="n">
-        <v>46.4</v>
+        <v>24.8</v>
       </c>
       <c r="E4" t="n">
-        <v>56.04</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>38.2</v>
       </c>
       <c r="D5" t="n">
-        <v>34.4</v>
+        <v>33.5</v>
       </c>
       <c r="E5" t="n">
-        <v>49.56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30.4</v>
+        <v>40.2</v>
       </c>
       <c r="D6" t="n">
-        <v>24.8</v>
+        <v>37.5</v>
       </c>
       <c r="E6" t="n">
-        <v>44.52</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38.2</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>33.5</v>
+        <v>25.2</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40.2</v>
+        <v>15.6</v>
       </c>
       <c r="D8" t="n">
-        <v>37.5</v>
+        <v>18.6</v>
       </c>
       <c r="E8" t="n">
-        <v>49.68</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>22.2</v>
       </c>
       <c r="D9" t="n">
-        <v>25.2</v>
+        <v>20.8</v>
       </c>
       <c r="E9" t="n">
-        <v>44.52</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.6</v>
+        <v>2.4</v>
       </c>
       <c r="D10" t="n">
-        <v>18.6</v>
+        <v>11.6</v>
       </c>
       <c r="E10" t="n">
-        <v>38.08</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,61 +656,61 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.2</v>
+        <v>-2.6</v>
       </c>
       <c r="D11" t="n">
-        <v>20.8</v>
+        <v>5.3</v>
       </c>
       <c r="E11" t="n">
-        <v>37.52</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.4</v>
+        <v>15.8</v>
       </c>
       <c r="D12" t="n">
-        <v>11.6</v>
+        <v>33.45</v>
       </c>
       <c r="E12" t="n">
-        <v>36.44</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-2.6</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>5.3</v>
+        <v>28.95</v>
       </c>
       <c r="E13" t="n">
-        <v>29.8</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15.8</v>
+        <v>2.2</v>
       </c>
       <c r="D14" t="n">
-        <v>33.45</v>
+        <v>25.85</v>
       </c>
       <c r="E14" t="n">
-        <v>36.83</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>28.95</v>
+        <v>23.6</v>
       </c>
       <c r="E15" t="n">
-        <v>33.37</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.2</v>
+        <v>-2</v>
       </c>
       <c r="D16" t="n">
-        <v>25.85</v>
+        <v>19.35</v>
       </c>
       <c r="E16" t="n">
-        <v>30.74</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>15.2</v>
       </c>
       <c r="D17" t="n">
-        <v>23.6</v>
+        <v>28.55</v>
       </c>
       <c r="E17" t="n">
-        <v>29.83</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-2</v>
+        <v>6.6</v>
       </c>
       <c r="D18" t="n">
-        <v>19.35</v>
+        <v>19.8</v>
       </c>
       <c r="E18" t="n">
-        <v>23.6</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="D19" t="n">
-        <v>28.55</v>
+        <v>12.1</v>
       </c>
       <c r="E19" t="n">
-        <v>32.14</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.6</v>
+        <v>13.6</v>
       </c>
       <c r="D20" t="n">
-        <v>19.8</v>
+        <v>17.05</v>
       </c>
       <c r="E20" t="n">
-        <v>26.26</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
       <c r="D21" t="n">
-        <v>12.1</v>
+        <v>19.3</v>
       </c>
       <c r="E21" t="n">
-        <v>22.03</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13.6</v>
+        <v>47.8</v>
       </c>
       <c r="D22" t="n">
-        <v>17.05</v>
+        <v>46.45</v>
       </c>
       <c r="E22" t="n">
-        <v>22.46</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="D23" t="n">
-        <v>19.3</v>
+        <v>26.55</v>
       </c>
       <c r="E23" t="n">
-        <v>23.89</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>47.8</v>
+        <v>7.4</v>
       </c>
       <c r="D24" t="n">
-        <v>46.45</v>
+        <v>26.25</v>
       </c>
       <c r="E24" t="n">
-        <v>43.43</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13.8</v>
+        <v>24.8</v>
       </c>
       <c r="D25" t="n">
-        <v>26.55</v>
+        <v>33.2</v>
       </c>
       <c r="E25" t="n">
-        <v>28.69</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7.4</v>
+        <v>23.2</v>
       </c>
       <c r="D26" t="n">
-        <v>26.25</v>
+        <v>31.25</v>
       </c>
       <c r="E26" t="n">
-        <v>30.86</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.8</v>
+        <v>10.4</v>
       </c>
       <c r="D27" t="n">
-        <v>33.2</v>
+        <v>26.7</v>
       </c>
       <c r="E27" t="n">
-        <v>34.97</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.2</v>
+        <v>18.2</v>
       </c>
       <c r="D28" t="n">
-        <v>31.25</v>
+        <v>29.95</v>
       </c>
       <c r="E28" t="n">
-        <v>34.37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="E29" t="n">
-        <v>32.4</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>18.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D30" t="n">
-        <v>29.95</v>
+        <v>24.55</v>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,61 +1076,61 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="E31" t="n">
-        <v>32.14</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.6</v>
+        <v>14.2</v>
       </c>
       <c r="D32" t="n">
-        <v>24.55</v>
+        <v>30.53</v>
       </c>
       <c r="E32" t="n">
-        <v>30.51</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8.199999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D33" t="n">
-        <v>29.4</v>
+        <v>36.67</v>
       </c>
       <c r="E33" t="n">
-        <v>33.54</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14.2</v>
+        <v>25.2</v>
       </c>
       <c r="D34" t="n">
-        <v>30.53</v>
+        <v>40.07</v>
       </c>
       <c r="E34" t="n">
-        <v>35.33</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="D35" t="n">
-        <v>36.67</v>
+        <v>41.67</v>
       </c>
       <c r="E35" t="n">
-        <v>39.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>25.2</v>
+        <v>51.4</v>
       </c>
       <c r="D36" t="n">
-        <v>40.07</v>
+        <v>43.33</v>
       </c>
       <c r="E36" t="n">
-        <v>44.87</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="D37" t="n">
-        <v>41.67</v>
+        <v>47.87</v>
       </c>
       <c r="E37" t="n">
-        <v>46</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>51.4</v>
+        <v>34.6</v>
       </c>
       <c r="D38" t="n">
-        <v>43.33</v>
+        <v>56</v>
       </c>
       <c r="E38" t="n">
-        <v>45.5</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>27.2</v>
+        <v>39.4</v>
       </c>
       <c r="D39" t="n">
-        <v>47.87</v>
+        <v>57.27</v>
       </c>
       <c r="E39" t="n">
-        <v>49.63</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>61.73</v>
       </c>
       <c r="E40" t="n">
-        <v>55.67</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="D41" t="n">
-        <v>57.27</v>
+        <v>51.53</v>
       </c>
       <c r="E41" t="n">
-        <v>57.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>47</v>
+        <v>43.2</v>
       </c>
       <c r="D42" t="n">
-        <v>61.73</v>
+        <v>53.53</v>
       </c>
       <c r="E42" t="n">
-        <v>60.87</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38.6</v>
+        <v>44.6</v>
       </c>
       <c r="D43" t="n">
-        <v>51.53</v>
+        <v>57.93</v>
       </c>
       <c r="E43" t="n">
-        <v>51.73</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>43.2</v>
+        <v>48.8</v>
       </c>
       <c r="D44" t="n">
-        <v>53.53</v>
+        <v>61</v>
       </c>
       <c r="E44" t="n">
-        <v>53.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="D45" t="n">
-        <v>57.93</v>
+        <v>58.33</v>
       </c>
       <c r="E45" t="n">
-        <v>55.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D46" t="n">
-        <v>61</v>
+        <v>63.4</v>
       </c>
       <c r="E46" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D47" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E47" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,61 +1433,61 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D48" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E48" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E49" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D51" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E51" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D52" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E52" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D53" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,34 +1559,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D54" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>66.2</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>IC2604</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="D55" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="E55" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47.8</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>46.4</v>
+        <v>34.4</v>
       </c>
       <c r="E2" t="n">
-        <v>56.04</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>30.4</v>
       </c>
       <c r="D3" t="n">
-        <v>34.4</v>
+        <v>24.8</v>
       </c>
       <c r="E3" t="n">
-        <v>49.56</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.4</v>
+        <v>38.2</v>
       </c>
       <c r="D4" t="n">
-        <v>24.8</v>
+        <v>33.5</v>
       </c>
       <c r="E4" t="n">
-        <v>44.52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.2</v>
+        <v>40.2</v>
       </c>
       <c r="D5" t="n">
-        <v>33.5</v>
+        <v>37.5</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.2</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>37.5</v>
+        <v>25.2</v>
       </c>
       <c r="E6" t="n">
-        <v>49.68</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>15.6</v>
       </c>
       <c r="D7" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="E7" t="n">
-        <v>44.52</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="D8" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="E8" t="n">
-        <v>38.08</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.2</v>
+        <v>2.4</v>
       </c>
       <c r="D9" t="n">
-        <v>20.8</v>
+        <v>11.6</v>
       </c>
       <c r="E9" t="n">
-        <v>37.52</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,40 +635,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="D10" t="n">
-        <v>11.6</v>
+        <v>5.3</v>
       </c>
       <c r="E10" t="n">
-        <v>36.44</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-2.6</v>
+        <v>15.8</v>
       </c>
       <c r="D11" t="n">
-        <v>5.3</v>
+        <v>33.45</v>
       </c>
       <c r="E11" t="n">
-        <v>29.8</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>33.45</v>
+        <v>28.95</v>
       </c>
       <c r="E12" t="n">
-        <v>36.83</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="D13" t="n">
-        <v>28.95</v>
+        <v>25.85</v>
       </c>
       <c r="E13" t="n">
-        <v>33.37</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="E14" t="n">
-        <v>30.74</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D15" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E15" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D16" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E16" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D17" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E17" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D18" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E18" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D19" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E19" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D20" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E20" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D21" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E21" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D22" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E22" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D23" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E23" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D24" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E24" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D25" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E25" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D26" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E26" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D27" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E27" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E28" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D29" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E29" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,40 +1055,40 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E30" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D31" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E31" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D32" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E32" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D33" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E33" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E34" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D35" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E35" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D36" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E36" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D37" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E37" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D38" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E38" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D39" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E39" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D40" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E40" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D41" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E41" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D42" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E42" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D43" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E43" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D44" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E44" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D45" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E45" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D46" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E46" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,40 +1412,40 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D47" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E47" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D48" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E48" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D50" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E50" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D51" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E51" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D52" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D53" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,13 +1559,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D54" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E54" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,6 +1568,27 @@
         <v>64.04000000000001</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="E55" t="n">
+        <v>61.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,27 @@
         <v>61.4</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1610,6 +1610,27 @@
         <v>65.59999999999999</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="D57" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="E57" t="n">
+        <v>65.76000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>38.2</v>
       </c>
       <c r="D2" t="n">
-        <v>34.4</v>
+        <v>33.5</v>
       </c>
       <c r="E2" t="n">
-        <v>49.56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.4</v>
+        <v>40.2</v>
       </c>
       <c r="D3" t="n">
-        <v>24.8</v>
+        <v>37.5</v>
       </c>
       <c r="E3" t="n">
-        <v>44.52</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.2</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>33.5</v>
+        <v>25.2</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.2</v>
+        <v>15.6</v>
       </c>
       <c r="D5" t="n">
-        <v>37.5</v>
+        <v>18.6</v>
       </c>
       <c r="E5" t="n">
-        <v>49.68</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>22.2</v>
       </c>
       <c r="D6" t="n">
-        <v>25.2</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="n">
-        <v>44.52</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.6</v>
+        <v>2.4</v>
       </c>
       <c r="D7" t="n">
-        <v>18.6</v>
+        <v>11.6</v>
       </c>
       <c r="E7" t="n">
-        <v>38.08</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,61 +593,61 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.2</v>
+        <v>-2.6</v>
       </c>
       <c r="D8" t="n">
-        <v>20.8</v>
+        <v>5.3</v>
       </c>
       <c r="E8" t="n">
-        <v>37.52</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.4</v>
+        <v>15.8</v>
       </c>
       <c r="D9" t="n">
-        <v>11.6</v>
+        <v>33.45</v>
       </c>
       <c r="E9" t="n">
-        <v>36.44</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-2.6</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>5.3</v>
+        <v>28.95</v>
       </c>
       <c r="E10" t="n">
-        <v>29.8</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.8</v>
+        <v>2.2</v>
       </c>
       <c r="D11" t="n">
-        <v>33.45</v>
+        <v>25.85</v>
       </c>
       <c r="E11" t="n">
-        <v>36.83</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>28.95</v>
+        <v>23.6</v>
       </c>
       <c r="E12" t="n">
-        <v>33.37</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.2</v>
+        <v>-2</v>
       </c>
       <c r="D13" t="n">
-        <v>25.85</v>
+        <v>19.35</v>
       </c>
       <c r="E13" t="n">
-        <v>30.74</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>15.2</v>
       </c>
       <c r="D14" t="n">
-        <v>23.6</v>
+        <v>28.55</v>
       </c>
       <c r="E14" t="n">
-        <v>29.83</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-2</v>
+        <v>6.6</v>
       </c>
       <c r="D15" t="n">
-        <v>19.35</v>
+        <v>19.8</v>
       </c>
       <c r="E15" t="n">
-        <v>23.6</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="D16" t="n">
-        <v>28.55</v>
+        <v>12.1</v>
       </c>
       <c r="E16" t="n">
-        <v>32.14</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.6</v>
+        <v>13.6</v>
       </c>
       <c r="D17" t="n">
-        <v>19.8</v>
+        <v>17.05</v>
       </c>
       <c r="E17" t="n">
-        <v>26.26</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
       <c r="D18" t="n">
-        <v>12.1</v>
+        <v>19.3</v>
       </c>
       <c r="E18" t="n">
-        <v>22.03</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13.6</v>
+        <v>47.8</v>
       </c>
       <c r="D19" t="n">
-        <v>17.05</v>
+        <v>46.45</v>
       </c>
       <c r="E19" t="n">
-        <v>22.46</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="D20" t="n">
-        <v>19.3</v>
+        <v>26.55</v>
       </c>
       <c r="E20" t="n">
-        <v>23.89</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>47.8</v>
+        <v>7.4</v>
       </c>
       <c r="D21" t="n">
-        <v>46.45</v>
+        <v>26.25</v>
       </c>
       <c r="E21" t="n">
-        <v>43.43</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13.8</v>
+        <v>24.8</v>
       </c>
       <c r="D22" t="n">
-        <v>26.55</v>
+        <v>33.2</v>
       </c>
       <c r="E22" t="n">
-        <v>28.69</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.4</v>
+        <v>23.2</v>
       </c>
       <c r="D23" t="n">
-        <v>26.25</v>
+        <v>31.25</v>
       </c>
       <c r="E23" t="n">
-        <v>30.86</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.8</v>
+        <v>10.4</v>
       </c>
       <c r="D24" t="n">
-        <v>33.2</v>
+        <v>26.7</v>
       </c>
       <c r="E24" t="n">
-        <v>34.97</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.2</v>
+        <v>18.2</v>
       </c>
       <c r="D25" t="n">
-        <v>31.25</v>
+        <v>29.95</v>
       </c>
       <c r="E25" t="n">
-        <v>34.37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="E26" t="n">
-        <v>32.4</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D27" t="n">
-        <v>29.95</v>
+        <v>24.55</v>
       </c>
       <c r="E27" t="n">
-        <v>35</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,61 +1013,61 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="E28" t="n">
-        <v>32.14</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.6</v>
+        <v>14.2</v>
       </c>
       <c r="D29" t="n">
-        <v>24.55</v>
+        <v>30.53</v>
       </c>
       <c r="E29" t="n">
-        <v>30.51</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.199999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D30" t="n">
-        <v>29.4</v>
+        <v>36.67</v>
       </c>
       <c r="E30" t="n">
-        <v>33.54</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14.2</v>
+        <v>25.2</v>
       </c>
       <c r="D31" t="n">
-        <v>30.53</v>
+        <v>40.07</v>
       </c>
       <c r="E31" t="n">
-        <v>35.33</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>36.67</v>
+        <v>41.67</v>
       </c>
       <c r="E32" t="n">
-        <v>39.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25.2</v>
+        <v>51.4</v>
       </c>
       <c r="D33" t="n">
-        <v>40.07</v>
+        <v>43.33</v>
       </c>
       <c r="E33" t="n">
-        <v>44.87</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="D34" t="n">
-        <v>41.67</v>
+        <v>47.87</v>
       </c>
       <c r="E34" t="n">
-        <v>46</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>51.4</v>
+        <v>34.6</v>
       </c>
       <c r="D35" t="n">
-        <v>43.33</v>
+        <v>56</v>
       </c>
       <c r="E35" t="n">
-        <v>45.5</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>27.2</v>
+        <v>39.4</v>
       </c>
       <c r="D36" t="n">
-        <v>47.87</v>
+        <v>57.27</v>
       </c>
       <c r="E36" t="n">
-        <v>49.63</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="D37" t="n">
-        <v>56</v>
+        <v>61.73</v>
       </c>
       <c r="E37" t="n">
-        <v>55.67</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="D38" t="n">
-        <v>57.27</v>
+        <v>51.53</v>
       </c>
       <c r="E38" t="n">
-        <v>57.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>47</v>
+        <v>43.2</v>
       </c>
       <c r="D39" t="n">
-        <v>61.73</v>
+        <v>53.53</v>
       </c>
       <c r="E39" t="n">
-        <v>60.87</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38.6</v>
+        <v>44.6</v>
       </c>
       <c r="D40" t="n">
-        <v>51.53</v>
+        <v>57.93</v>
       </c>
       <c r="E40" t="n">
-        <v>51.73</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>43.2</v>
+        <v>48.8</v>
       </c>
       <c r="D41" t="n">
-        <v>53.53</v>
+        <v>61</v>
       </c>
       <c r="E41" t="n">
-        <v>53.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="D42" t="n">
-        <v>57.93</v>
+        <v>58.33</v>
       </c>
       <c r="E42" t="n">
-        <v>55.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>61</v>
+        <v>63.4</v>
       </c>
       <c r="E43" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D44" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E44" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,61 +1370,61 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D45" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E45" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D46" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E46" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D48" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E48" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D49" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E49" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D50" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D51" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1520,16 +1520,16 @@
         <v>49.2</v>
       </c>
       <c r="D52" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E52" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D53" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D54" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E54" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,54 +1580,12 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D55" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>IC2604</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="D56" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="E56" t="n">
-        <v>65.59999999999999</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>IC2604</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="D57" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="E57" t="n">
         <v>65.76000000000001</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38.2</v>
+        <v>40.2</v>
       </c>
       <c r="D2" t="n">
-        <v>33.5</v>
+        <v>37.5</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.2</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>37.5</v>
+        <v>25.2</v>
       </c>
       <c r="E3" t="n">
-        <v>49.68</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>15.6</v>
       </c>
       <c r="D4" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="E4" t="n">
-        <v>44.52</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="D5" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="n">
-        <v>38.08</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.2</v>
+        <v>2.4</v>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>11.6</v>
       </c>
       <c r="E6" t="n">
-        <v>37.52</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,40 +572,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="D7" t="n">
-        <v>11.6</v>
+        <v>5.3</v>
       </c>
       <c r="E7" t="n">
-        <v>36.44</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.6</v>
+        <v>15.8</v>
       </c>
       <c r="D8" t="n">
-        <v>5.3</v>
+        <v>33.45</v>
       </c>
       <c r="E8" t="n">
-        <v>29.8</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>33.45</v>
+        <v>28.95</v>
       </c>
       <c r="E9" t="n">
-        <v>36.83</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="D10" t="n">
-        <v>28.95</v>
+        <v>25.85</v>
       </c>
       <c r="E10" t="n">
-        <v>33.37</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="E11" t="n">
-        <v>30.74</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D12" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E12" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D13" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E13" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D14" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E14" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D15" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E15" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D16" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E16" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D17" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E17" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D18" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E18" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D19" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E19" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D20" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E20" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D21" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E21" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D22" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E22" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D23" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E23" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D24" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E24" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D26" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E26" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,40 +992,40 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E27" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D28" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E28" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D29" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E29" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D30" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E30" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E31" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D32" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E32" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D33" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E33" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D34" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E34" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D35" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E35" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D36" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E36" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D37" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E37" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D38" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E38" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D39" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E39" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D40" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E40" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D41" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E41" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E42" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D43" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E43" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,40 +1349,40 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D44" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E44" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D45" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E45" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D47" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E47" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D48" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E48" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D49" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D50" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D51" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E51" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D52" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D53" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E53" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D54" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D55" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E55" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.2</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>37.5</v>
+        <v>25.2</v>
       </c>
       <c r="E2" t="n">
-        <v>49.68</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>15.6</v>
       </c>
       <c r="D3" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="E3" t="n">
-        <v>44.52</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="D4" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="n">
-        <v>38.08</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.2</v>
+        <v>2.4</v>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>11.6</v>
       </c>
       <c r="E5" t="n">
-        <v>37.52</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,40 +551,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="D6" t="n">
-        <v>11.6</v>
+        <v>5.3</v>
       </c>
       <c r="E6" t="n">
-        <v>36.44</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-2.6</v>
+        <v>15.8</v>
       </c>
       <c r="D7" t="n">
-        <v>5.3</v>
+        <v>33.45</v>
       </c>
       <c r="E7" t="n">
-        <v>29.8</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>33.45</v>
+        <v>28.95</v>
       </c>
       <c r="E8" t="n">
-        <v>36.83</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95</v>
+        <v>25.85</v>
       </c>
       <c r="E9" t="n">
-        <v>33.37</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="E10" t="n">
-        <v>30.74</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D11" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E11" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E11" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D12" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E12" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D13" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E13" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D14" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E14" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D15" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E15" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D16" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E16" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D17" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E17" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D18" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E18" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D19" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E19" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D20" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E20" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D21" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E21" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D22" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E22" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D23" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E23" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E24" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D25" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E25" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,40 +971,40 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E26" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D27" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E27" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D28" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E28" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D29" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E29" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E30" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D31" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E31" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D32" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E32" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D33" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E33" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D34" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E34" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D35" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E35" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D36" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E36" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D37" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E37" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D38" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E38" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D39" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D40" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E40" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D41" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E41" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D42" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E42" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,40 +1328,40 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D43" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E43" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D44" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E44" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D46" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E46" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D47" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E47" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D48" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D49" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D50" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E50" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D51" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D52" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E52" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D53" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D54" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E54" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D55" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E55" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>15.6</v>
       </c>
       <c r="D2" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="E2" t="n">
-        <v>44.52</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="D3" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="n">
-        <v>38.08</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.2</v>
+        <v>2.4</v>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>11.6</v>
       </c>
       <c r="E4" t="n">
-        <v>37.52</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,40 +530,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="D5" t="n">
-        <v>11.6</v>
+        <v>5.3</v>
       </c>
       <c r="E5" t="n">
-        <v>36.44</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-2.6</v>
+        <v>15.8</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3</v>
+        <v>33.45</v>
       </c>
       <c r="E6" t="n">
-        <v>29.8</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>33.45</v>
+        <v>28.95</v>
       </c>
       <c r="E7" t="n">
-        <v>36.83</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95</v>
+        <v>25.85</v>
       </c>
       <c r="E8" t="n">
-        <v>33.37</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="E9" t="n">
-        <v>30.74</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D10" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E10" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D11" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E11" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D12" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E12" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E13" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D14" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E14" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D15" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E15" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D16" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E16" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D17" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E17" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D18" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E18" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D19" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E19" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D20" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E20" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D21" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E21" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D22" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E22" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E23" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D24" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E24" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,40 +950,40 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E25" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D26" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E26" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D27" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E27" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D28" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E28" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E29" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D30" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E30" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D31" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E31" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D32" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E32" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D33" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E33" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D34" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E34" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D35" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E35" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D36" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E36" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D37" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E37" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D38" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E38" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E39" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D40" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E40" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D41" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E41" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,40 +1307,40 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D42" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E42" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E43" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D45" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E45" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D46" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E46" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D47" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D48" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D49" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E49" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D50" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D51" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E51" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D52" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D53" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E53" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D54" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E54" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D55" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,27 @@
         <v>62</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E56" t="n">
+        <v>59.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.6</v>
+        <v>2.4</v>
       </c>
       <c r="D2" t="n">
-        <v>18.6</v>
+        <v>11.6</v>
       </c>
       <c r="E2" t="n">
-        <v>38.08</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.2</v>
+        <v>-2.6</v>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>5.3</v>
       </c>
       <c r="E3" t="n">
-        <v>37.52</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.4</v>
+        <v>15.8</v>
       </c>
       <c r="D4" t="n">
-        <v>11.6</v>
+        <v>33.45</v>
       </c>
       <c r="E4" t="n">
-        <v>36.44</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-2.6</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3</v>
+        <v>28.95</v>
       </c>
       <c r="E5" t="n">
-        <v>29.8</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.8</v>
+        <v>2.2</v>
       </c>
       <c r="D6" t="n">
-        <v>33.45</v>
+        <v>25.85</v>
       </c>
       <c r="E6" t="n">
-        <v>36.83</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>28.95</v>
+        <v>23.6</v>
       </c>
       <c r="E7" t="n">
-        <v>33.37</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2</v>
+        <v>-2</v>
       </c>
       <c r="D8" t="n">
-        <v>25.85</v>
+        <v>19.35</v>
       </c>
       <c r="E8" t="n">
-        <v>30.74</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>15.2</v>
       </c>
       <c r="D9" t="n">
-        <v>23.6</v>
+        <v>28.55</v>
       </c>
       <c r="E9" t="n">
-        <v>29.83</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-2</v>
+        <v>6.6</v>
       </c>
       <c r="D10" t="n">
-        <v>19.35</v>
+        <v>19.8</v>
       </c>
       <c r="E10" t="n">
-        <v>23.6</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="D11" t="n">
-        <v>28.55</v>
+        <v>12.1</v>
       </c>
       <c r="E11" t="n">
-        <v>32.14</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.6</v>
+        <v>13.6</v>
       </c>
       <c r="D12" t="n">
-        <v>19.8</v>
+        <v>17.05</v>
       </c>
       <c r="E12" t="n">
-        <v>26.26</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
       <c r="D13" t="n">
-        <v>12.1</v>
+        <v>19.3</v>
       </c>
       <c r="E13" t="n">
-        <v>22.03</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13.6</v>
+        <v>47.8</v>
       </c>
       <c r="D14" t="n">
-        <v>17.05</v>
+        <v>46.45</v>
       </c>
       <c r="E14" t="n">
-        <v>22.46</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="D15" t="n">
-        <v>19.3</v>
+        <v>26.55</v>
       </c>
       <c r="E15" t="n">
-        <v>23.89</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>47.8</v>
+        <v>7.4</v>
       </c>
       <c r="D16" t="n">
-        <v>46.45</v>
+        <v>26.25</v>
       </c>
       <c r="E16" t="n">
-        <v>43.43</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13.8</v>
+        <v>24.8</v>
       </c>
       <c r="D17" t="n">
-        <v>26.55</v>
+        <v>33.2</v>
       </c>
       <c r="E17" t="n">
-        <v>28.69</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.4</v>
+        <v>23.2</v>
       </c>
       <c r="D18" t="n">
-        <v>26.25</v>
+        <v>31.25</v>
       </c>
       <c r="E18" t="n">
-        <v>30.86</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.8</v>
+        <v>10.4</v>
       </c>
       <c r="D19" t="n">
-        <v>33.2</v>
+        <v>26.7</v>
       </c>
       <c r="E19" t="n">
-        <v>34.97</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.2</v>
+        <v>18.2</v>
       </c>
       <c r="D20" t="n">
-        <v>31.25</v>
+        <v>29.95</v>
       </c>
       <c r="E20" t="n">
-        <v>34.37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="E21" t="n">
-        <v>32.4</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D22" t="n">
-        <v>29.95</v>
+        <v>24.55</v>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,61 +908,61 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="E23" t="n">
-        <v>32.14</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.6</v>
+        <v>14.2</v>
       </c>
       <c r="D24" t="n">
-        <v>24.55</v>
+        <v>30.53</v>
       </c>
       <c r="E24" t="n">
-        <v>30.51</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.199999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D25" t="n">
-        <v>29.4</v>
+        <v>36.67</v>
       </c>
       <c r="E25" t="n">
-        <v>33.54</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14.2</v>
+        <v>25.2</v>
       </c>
       <c r="D26" t="n">
-        <v>30.53</v>
+        <v>40.07</v>
       </c>
       <c r="E26" t="n">
-        <v>35.33</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>36.67</v>
+        <v>41.67</v>
       </c>
       <c r="E27" t="n">
-        <v>39.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.2</v>
+        <v>51.4</v>
       </c>
       <c r="D28" t="n">
-        <v>40.07</v>
+        <v>43.33</v>
       </c>
       <c r="E28" t="n">
-        <v>44.87</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="D29" t="n">
-        <v>41.67</v>
+        <v>47.87</v>
       </c>
       <c r="E29" t="n">
-        <v>46</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>51.4</v>
+        <v>34.6</v>
       </c>
       <c r="D30" t="n">
-        <v>43.33</v>
+        <v>56</v>
       </c>
       <c r="E30" t="n">
-        <v>45.5</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.2</v>
+        <v>39.4</v>
       </c>
       <c r="D31" t="n">
-        <v>47.87</v>
+        <v>57.27</v>
       </c>
       <c r="E31" t="n">
-        <v>49.63</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="D32" t="n">
-        <v>56</v>
+        <v>61.73</v>
       </c>
       <c r="E32" t="n">
-        <v>55.67</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="D33" t="n">
-        <v>57.27</v>
+        <v>51.53</v>
       </c>
       <c r="E33" t="n">
-        <v>57.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>47</v>
+        <v>43.2</v>
       </c>
       <c r="D34" t="n">
-        <v>61.73</v>
+        <v>53.53</v>
       </c>
       <c r="E34" t="n">
-        <v>60.87</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38.6</v>
+        <v>44.6</v>
       </c>
       <c r="D35" t="n">
-        <v>51.53</v>
+        <v>57.93</v>
       </c>
       <c r="E35" t="n">
-        <v>51.73</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>43.2</v>
+        <v>48.8</v>
       </c>
       <c r="D36" t="n">
-        <v>53.53</v>
+        <v>61</v>
       </c>
       <c r="E36" t="n">
-        <v>53.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="D37" t="n">
-        <v>57.93</v>
+        <v>58.33</v>
       </c>
       <c r="E37" t="n">
-        <v>55.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D38" t="n">
-        <v>61</v>
+        <v>63.4</v>
       </c>
       <c r="E38" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D39" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E39" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,61 +1265,61 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D40" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E40" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D41" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E41" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D43" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E43" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D44" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E44" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D45" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D46" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1415,16 +1415,16 @@
         <v>49.2</v>
       </c>
       <c r="D47" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E47" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D48" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D49" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E49" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D50" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D51" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E51" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D52" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E52" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D53" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D54" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>56.48</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,34 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
       <c r="D55" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E55" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>IC2604</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="D56" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="E56" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,40 +467,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6</v>
+        <v>5.3</v>
       </c>
       <c r="E2" t="n">
-        <v>36.44</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-2.6</v>
+        <v>15.8</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3</v>
+        <v>33.45</v>
       </c>
       <c r="E3" t="n">
-        <v>29.8</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>33.45</v>
+        <v>28.95</v>
       </c>
       <c r="E4" t="n">
-        <v>36.83</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="D5" t="n">
-        <v>28.95</v>
+        <v>25.85</v>
       </c>
       <c r="E5" t="n">
-        <v>33.37</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="E6" t="n">
-        <v>30.74</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D7" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E7" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D8" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E8" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D9" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E9" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D10" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E10" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D11" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E11" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D12" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E12" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D13" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E13" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D14" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E14" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D15" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E15" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D16" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E16" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D17" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E17" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D18" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E18" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D19" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E19" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D21" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E21" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E22" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D23" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E23" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D24" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E24" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D25" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E25" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E26" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D27" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E27" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D28" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E28" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D29" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D30" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E30" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D31" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E31" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D32" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E32" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D33" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E33" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D34" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E34" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D35" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E35" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D36" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E36" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D37" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E37" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D38" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E38" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,40 +1244,40 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D39" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E39" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D40" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E40" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D42" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E42" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D43" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E43" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D44" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D45" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D46" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E46" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D47" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D48" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E48" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D49" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D50" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E50" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D51" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E51" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D52" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D53" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D54" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E54" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D55" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E55" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,28 +458,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IC2601</t>
+          <t>IC2602</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.6</v>
+        <v>15.8</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3</v>
+        <v>33.45</v>
       </c>
       <c r="E2" t="n">
-        <v>29.8</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>33.45</v>
+        <v>28.95</v>
       </c>
       <c r="E3" t="n">
-        <v>36.83</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="D4" t="n">
-        <v>28.95</v>
+        <v>25.85</v>
       </c>
       <c r="E4" t="n">
-        <v>33.37</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="E5" t="n">
-        <v>30.74</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D6" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E6" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D7" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E7" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D8" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E8" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E9" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D10" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E10" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D11" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E11" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D12" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E12" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D13" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E13" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D14" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E14" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D15" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E15" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D16" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E16" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D17" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E17" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D18" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E18" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D20" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E20" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,40 +866,40 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E21" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D22" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E22" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D23" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E23" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D24" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E24" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E25" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D26" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E26" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D27" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E27" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D28" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E28" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E29" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D30" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E30" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D31" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E31" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D32" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E32" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D33" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E33" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D34" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E34" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D35" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E35" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D36" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E36" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D37" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E37" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,40 +1223,40 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D38" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E38" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D39" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E39" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D41" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E41" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D42" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E42" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D43" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D44" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D45" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E45" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D46" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D47" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E47" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D48" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D49" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E49" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D50" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E50" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D51" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D52" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D53" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E53" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D54" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E54" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D55" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E55" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,27 @@
         <v>58.08</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IC2604</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>27</v>
+      </c>
+      <c r="D56" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>52.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.8</v>
+        <v>2.2</v>
       </c>
       <c r="D2" t="n">
-        <v>33.45</v>
+        <v>25.85</v>
       </c>
       <c r="E2" t="n">
-        <v>36.83</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>28.95</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="n">
-        <v>33.37</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.2</v>
+        <v>-2</v>
       </c>
       <c r="D4" t="n">
-        <v>25.85</v>
+        <v>19.35</v>
       </c>
       <c r="E4" t="n">
-        <v>30.74</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>15.2</v>
       </c>
       <c r="D5" t="n">
-        <v>23.6</v>
+        <v>28.55</v>
       </c>
       <c r="E5" t="n">
-        <v>29.83</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-2</v>
+        <v>6.6</v>
       </c>
       <c r="D6" t="n">
-        <v>19.35</v>
+        <v>19.8</v>
       </c>
       <c r="E6" t="n">
-        <v>23.6</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="D7" t="n">
-        <v>28.55</v>
+        <v>12.1</v>
       </c>
       <c r="E7" t="n">
-        <v>32.14</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.6</v>
+        <v>13.6</v>
       </c>
       <c r="D8" t="n">
-        <v>19.8</v>
+        <v>17.05</v>
       </c>
       <c r="E8" t="n">
-        <v>26.26</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
       <c r="D9" t="n">
-        <v>12.1</v>
+        <v>19.3</v>
       </c>
       <c r="E9" t="n">
-        <v>22.03</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.6</v>
+        <v>47.8</v>
       </c>
       <c r="D10" t="n">
-        <v>17.05</v>
+        <v>46.45</v>
       </c>
       <c r="E10" t="n">
-        <v>22.46</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="D11" t="n">
-        <v>19.3</v>
+        <v>26.55</v>
       </c>
       <c r="E11" t="n">
-        <v>23.89</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>47.8</v>
+        <v>7.4</v>
       </c>
       <c r="D12" t="n">
-        <v>46.45</v>
+        <v>26.25</v>
       </c>
       <c r="E12" t="n">
-        <v>43.43</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13.8</v>
+        <v>24.8</v>
       </c>
       <c r="D13" t="n">
-        <v>26.55</v>
+        <v>33.2</v>
       </c>
       <c r="E13" t="n">
-        <v>28.69</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.4</v>
+        <v>23.2</v>
       </c>
       <c r="D14" t="n">
-        <v>26.25</v>
+        <v>31.25</v>
       </c>
       <c r="E14" t="n">
-        <v>30.86</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.8</v>
+        <v>10.4</v>
       </c>
       <c r="D15" t="n">
-        <v>33.2</v>
+        <v>26.7</v>
       </c>
       <c r="E15" t="n">
-        <v>34.97</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.2</v>
+        <v>18.2</v>
       </c>
       <c r="D16" t="n">
-        <v>31.25</v>
+        <v>29.95</v>
       </c>
       <c r="E16" t="n">
-        <v>34.37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="E17" t="n">
-        <v>32.4</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D18" t="n">
-        <v>29.95</v>
+        <v>24.55</v>
       </c>
       <c r="E18" t="n">
-        <v>35</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,61 +824,61 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="E19" t="n">
-        <v>32.14</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.6</v>
+        <v>14.2</v>
       </c>
       <c r="D20" t="n">
-        <v>24.55</v>
+        <v>30.53</v>
       </c>
       <c r="E20" t="n">
-        <v>30.51</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.199999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D21" t="n">
-        <v>29.4</v>
+        <v>36.67</v>
       </c>
       <c r="E21" t="n">
-        <v>33.54</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14.2</v>
+        <v>25.2</v>
       </c>
       <c r="D22" t="n">
-        <v>30.53</v>
+        <v>40.07</v>
       </c>
       <c r="E22" t="n">
-        <v>35.33</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>36.67</v>
+        <v>41.67</v>
       </c>
       <c r="E23" t="n">
-        <v>39.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.2</v>
+        <v>51.4</v>
       </c>
       <c r="D24" t="n">
-        <v>40.07</v>
+        <v>43.33</v>
       </c>
       <c r="E24" t="n">
-        <v>44.87</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="D25" t="n">
-        <v>41.67</v>
+        <v>47.87</v>
       </c>
       <c r="E25" t="n">
-        <v>46</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>51.4</v>
+        <v>34.6</v>
       </c>
       <c r="D26" t="n">
-        <v>43.33</v>
+        <v>56</v>
       </c>
       <c r="E26" t="n">
-        <v>45.5</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.2</v>
+        <v>39.4</v>
       </c>
       <c r="D27" t="n">
-        <v>47.87</v>
+        <v>57.27</v>
       </c>
       <c r="E27" t="n">
-        <v>49.63</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>61.73</v>
       </c>
       <c r="E28" t="n">
-        <v>55.67</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="D29" t="n">
-        <v>57.27</v>
+        <v>51.53</v>
       </c>
       <c r="E29" t="n">
-        <v>57.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>47</v>
+        <v>43.2</v>
       </c>
       <c r="D30" t="n">
-        <v>61.73</v>
+        <v>53.53</v>
       </c>
       <c r="E30" t="n">
-        <v>60.87</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38.6</v>
+        <v>44.6</v>
       </c>
       <c r="D31" t="n">
-        <v>51.53</v>
+        <v>57.93</v>
       </c>
       <c r="E31" t="n">
-        <v>51.73</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>43.2</v>
+        <v>48.8</v>
       </c>
       <c r="D32" t="n">
-        <v>53.53</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>53.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="D33" t="n">
-        <v>57.93</v>
+        <v>58.33</v>
       </c>
       <c r="E33" t="n">
-        <v>55.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>63.4</v>
       </c>
       <c r="E34" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D35" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E35" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,61 +1181,61 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D36" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E36" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D37" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E37" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D39" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E39" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D40" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E40" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D41" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D42" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1331,16 +1331,16 @@
         <v>49.2</v>
       </c>
       <c r="D43" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E43" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D44" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D45" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E45" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D46" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D47" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E47" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D48" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E48" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D49" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D50" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>56.48</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
       <c r="D51" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E51" t="n">
-        <v>62</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>40.2</v>
+        <v>47.4</v>
       </c>
       <c r="D52" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E52" t="n">
-        <v>59.52</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>50.4</v>
+        <v>46.8</v>
       </c>
       <c r="D53" t="n">
-        <v>71.5</v>
+        <v>67.5</v>
       </c>
       <c r="E53" t="n">
-        <v>61.32</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,55 +1559,34 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>47.4</v>
+        <v>27</v>
       </c>
       <c r="D54" t="n">
-        <v>70.5</v>
+        <v>56.5</v>
       </c>
       <c r="E54" t="n">
-        <v>60.68</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>46.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="E55" t="n">
-        <v>58.08</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>IC2604</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>27</v>
-      </c>
-      <c r="D56" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="E56" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>25.85</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="n">
-        <v>30.74</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D3" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E3" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D4" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E4" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D5" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E5" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D6" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E6" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D7" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E7" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D8" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E8" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D9" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E9" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D10" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E10" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D11" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E11" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D12" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E12" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D13" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E13" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D14" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E14" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D15" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E15" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D17" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E17" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,40 +803,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E18" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D19" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E19" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D20" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E20" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D21" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E21" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E22" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D23" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E23" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D24" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E24" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D25" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E25" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E26" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D27" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E27" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D28" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E28" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D29" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E29" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D30" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E30" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D31" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E32" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D33" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E33" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D34" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E34" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,40 +1160,40 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D35" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E35" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D36" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E36" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D38" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E38" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D39" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E39" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D40" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D41" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D42" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E42" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D43" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D44" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E44" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D45" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D46" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E46" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D47" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E47" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D48" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D49" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D50" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E50" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D51" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E51" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D52" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E52" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,40 +1538,40 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D53" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E53" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E54" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E55" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D2" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E2" t="n">
         <v>23.6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D3" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E3" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D4" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E4" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D5" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E5" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D6" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E6" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D7" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E7" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D8" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E8" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D9" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E9" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D10" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E10" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D11" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E11" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D12" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E12" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D13" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E13" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D14" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E14" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E16" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,40 +782,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E17" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D18" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E18" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D19" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E19" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D20" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E20" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E21" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D22" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D23" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E23" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D24" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E24" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D25" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E25" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D26" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E26" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D27" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E27" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D28" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E28" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D29" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E29" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D30" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E31" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E32" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D33" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E33" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,40 +1139,40 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D34" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E34" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D35" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E35" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D37" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E37" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D38" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E38" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D39" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D40" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D41" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E41" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D42" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D43" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E43" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D44" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D45" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E45" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D46" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E46" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D47" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D48" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D49" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E49" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D50" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E50" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D51" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E51" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,40 +1517,40 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D52" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E52" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E53" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E54" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E55" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2</v>
+        <v>15.2</v>
       </c>
       <c r="D2" t="n">
-        <v>19.35</v>
+        <v>28.55</v>
       </c>
       <c r="E2" t="n">
-        <v>23.6</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="D3" t="n">
-        <v>28.55</v>
+        <v>19.8</v>
       </c>
       <c r="E3" t="n">
-        <v>32.14</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="E4" t="n">
-        <v>26.26</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D5" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E5" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D6" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E6" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D7" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E7" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D8" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E8" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D9" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E9" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D10" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E10" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E11" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D12" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E12" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D13" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E13" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D15" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E15" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,40 +761,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E16" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D17" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E17" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D18" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E18" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D19" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E19" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E20" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D21" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E21" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D22" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E22" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D23" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E24" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D25" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E25" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D26" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E26" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D27" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E27" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D28" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E28" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D29" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E30" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D31" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E31" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D32" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E32" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,40 +1118,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D33" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E33" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D34" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E34" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D36" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E36" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D37" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E37" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D38" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D39" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D40" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E40" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D41" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D42" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E42" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D43" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D44" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E44" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D45" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E45" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D46" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D47" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D48" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E48" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D49" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E49" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D50" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E50" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,40 +1496,40 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D51" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E51" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E52" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E53" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E54" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D55" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E55" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,27 @@
         <v>53.71</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IC2605</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="D56" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="E56" t="n">
+        <v>53.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="D2" t="n">
-        <v>28.55</v>
+        <v>12.1</v>
       </c>
       <c r="E2" t="n">
-        <v>32.14</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.6</v>
+        <v>13.6</v>
       </c>
       <c r="D3" t="n">
-        <v>19.8</v>
+        <v>17.05</v>
       </c>
       <c r="E3" t="n">
-        <v>26.26</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
       <c r="D4" t="n">
-        <v>12.1</v>
+        <v>19.3</v>
       </c>
       <c r="E4" t="n">
-        <v>22.03</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.6</v>
+        <v>47.8</v>
       </c>
       <c r="D5" t="n">
-        <v>17.05</v>
+        <v>46.45</v>
       </c>
       <c r="E5" t="n">
-        <v>22.46</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="D6" t="n">
-        <v>19.3</v>
+        <v>26.55</v>
       </c>
       <c r="E6" t="n">
-        <v>23.89</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47.8</v>
+        <v>7.4</v>
       </c>
       <c r="D7" t="n">
-        <v>46.45</v>
+        <v>26.25</v>
       </c>
       <c r="E7" t="n">
-        <v>43.43</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13.8</v>
+        <v>24.8</v>
       </c>
       <c r="D8" t="n">
-        <v>26.55</v>
+        <v>33.2</v>
       </c>
       <c r="E8" t="n">
-        <v>28.69</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.4</v>
+        <v>23.2</v>
       </c>
       <c r="D9" t="n">
-        <v>26.25</v>
+        <v>31.25</v>
       </c>
       <c r="E9" t="n">
-        <v>30.86</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.8</v>
+        <v>10.4</v>
       </c>
       <c r="D10" t="n">
-        <v>33.2</v>
+        <v>26.7</v>
       </c>
       <c r="E10" t="n">
-        <v>34.97</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>18.2</v>
       </c>
       <c r="D11" t="n">
-        <v>31.25</v>
+        <v>29.95</v>
       </c>
       <c r="E11" t="n">
-        <v>34.37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="E12" t="n">
-        <v>32.4</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D13" t="n">
-        <v>29.95</v>
+        <v>24.55</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,61 +719,61 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="E14" t="n">
-        <v>32.14</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.6</v>
+        <v>14.2</v>
       </c>
       <c r="D15" t="n">
-        <v>24.55</v>
+        <v>30.53</v>
       </c>
       <c r="E15" t="n">
-        <v>30.51</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.199999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D16" t="n">
-        <v>29.4</v>
+        <v>36.67</v>
       </c>
       <c r="E16" t="n">
-        <v>33.54</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14.2</v>
+        <v>25.2</v>
       </c>
       <c r="D17" t="n">
-        <v>30.53</v>
+        <v>40.07</v>
       </c>
       <c r="E17" t="n">
-        <v>35.33</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>36.67</v>
+        <v>41.67</v>
       </c>
       <c r="E18" t="n">
-        <v>39.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25.2</v>
+        <v>51.4</v>
       </c>
       <c r="D19" t="n">
-        <v>40.07</v>
+        <v>43.33</v>
       </c>
       <c r="E19" t="n">
-        <v>44.87</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="D20" t="n">
-        <v>41.67</v>
+        <v>47.87</v>
       </c>
       <c r="E20" t="n">
-        <v>46</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>51.4</v>
+        <v>34.6</v>
       </c>
       <c r="D21" t="n">
-        <v>43.33</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
-        <v>45.5</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.2</v>
+        <v>39.4</v>
       </c>
       <c r="D22" t="n">
-        <v>47.87</v>
+        <v>57.27</v>
       </c>
       <c r="E22" t="n">
-        <v>49.63</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>61.73</v>
       </c>
       <c r="E23" t="n">
-        <v>55.67</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="D24" t="n">
-        <v>57.27</v>
+        <v>51.53</v>
       </c>
       <c r="E24" t="n">
-        <v>57.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>47</v>
+        <v>43.2</v>
       </c>
       <c r="D25" t="n">
-        <v>61.73</v>
+        <v>53.53</v>
       </c>
       <c r="E25" t="n">
-        <v>60.87</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38.6</v>
+        <v>44.6</v>
       </c>
       <c r="D26" t="n">
-        <v>51.53</v>
+        <v>57.93</v>
       </c>
       <c r="E26" t="n">
-        <v>51.73</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>43.2</v>
+        <v>48.8</v>
       </c>
       <c r="D27" t="n">
-        <v>53.53</v>
+        <v>61</v>
       </c>
       <c r="E27" t="n">
-        <v>53.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="D28" t="n">
-        <v>57.93</v>
+        <v>58.33</v>
       </c>
       <c r="E28" t="n">
-        <v>55.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>63.4</v>
       </c>
       <c r="E29" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D30" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E30" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,61 +1076,61 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D31" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E31" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E32" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D34" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E34" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D35" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E35" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D36" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D37" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>49.2</v>
       </c>
       <c r="D38" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E38" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D39" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D40" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E40" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D41" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D42" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E42" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D43" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E43" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D44" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D45" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>56.48</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
       <c r="D46" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E46" t="n">
-        <v>62</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>40.2</v>
+        <v>47.4</v>
       </c>
       <c r="D47" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E47" t="n">
-        <v>59.52</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>50.4</v>
+        <v>46.8</v>
       </c>
       <c r="D48" t="n">
-        <v>71.5</v>
+        <v>67.5</v>
       </c>
       <c r="E48" t="n">
-        <v>61.32</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,61 +1454,61 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>47.4</v>
+        <v>27</v>
       </c>
       <c r="D49" t="n">
-        <v>70.5</v>
+        <v>56.5</v>
       </c>
       <c r="E49" t="n">
-        <v>60.68</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>46.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="E50" t="n">
-        <v>58.08</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>27</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>56.5</v>
+        <v>60.6</v>
       </c>
       <c r="E51" t="n">
-        <v>52.96</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>90.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>61.1</v>
+        <v>59.45</v>
       </c>
       <c r="E52" t="n">
-        <v>54.06</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>91.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D53" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E53" t="n">
-        <v>54.77</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
       <c r="E54" t="n">
-        <v>54.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,34 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>88.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>59.3</v>
+        <v>56.65</v>
       </c>
       <c r="E55" t="n">
-        <v>53.71</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>IC2605</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="D56" t="n">
-        <v>57.85</v>
-      </c>
-      <c r="E56" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1</v>
+        <v>17.05</v>
       </c>
       <c r="E2" t="n">
-        <v>22.03</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D3" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E3" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D4" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E4" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D5" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E5" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D6" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E6" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D7" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E7" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D8" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E8" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D9" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E9" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D10" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E10" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D12" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E12" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,40 +698,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E13" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D14" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E14" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D15" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E15" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D16" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E16" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E17" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D18" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E18" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D19" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E19" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D20" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E20" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E21" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D22" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E22" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D23" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E23" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D24" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E24" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D25" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E25" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D26" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E26" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E27" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D28" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E28" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D29" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E29" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,40 +1055,40 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D30" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E30" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D31" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E31" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D33" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E33" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D34" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E34" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D35" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D36" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D37" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E37" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D38" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D39" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E39" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D40" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D41" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E41" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D42" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E42" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D43" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D44" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D45" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E45" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D46" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E46" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D47" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E47" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,40 +1433,40 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D48" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E48" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E49" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E50" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E51" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D52" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E52" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E53" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E54" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D55" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E55" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="D2" t="n">
-        <v>17.05</v>
+        <v>19.3</v>
       </c>
       <c r="E2" t="n">
-        <v>22.46</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D3" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E3" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D4" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E4" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D5" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E5" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D6" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E6" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D7" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E7" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D8" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E8" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D9" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E9" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D11" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E11" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,40 +677,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E12" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D13" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E13" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D14" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E14" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D15" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E15" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E16" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D17" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E17" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E18" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D19" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E19" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E20" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D21" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E21" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D22" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E22" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D23" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E23" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D24" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E24" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D25" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E25" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E26" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D27" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E27" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D28" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E28" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,40 +1034,40 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D29" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E29" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D30" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E30" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D32" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E32" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D33" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E33" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D34" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D35" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D36" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E36" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D37" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D38" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E38" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D39" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D40" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E40" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D41" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E41" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D42" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D43" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D44" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E44" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D45" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E45" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D46" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E46" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,40 +1412,40 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D47" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E47" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E48" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E49" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E50" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D51" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E51" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E52" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E53" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D54" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E54" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E55" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14.8</v>
+        <v>47.8</v>
       </c>
       <c r="D2" t="n">
-        <v>19.3</v>
+        <v>46.45</v>
       </c>
       <c r="E2" t="n">
-        <v>23.89</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47.8</v>
+        <v>13.8</v>
       </c>
       <c r="D3" t="n">
-        <v>46.45</v>
+        <v>26.55</v>
       </c>
       <c r="E3" t="n">
-        <v>43.43</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13.8</v>
+        <v>7.4</v>
       </c>
       <c r="D4" t="n">
-        <v>26.55</v>
+        <v>26.25</v>
       </c>
       <c r="E4" t="n">
-        <v>28.69</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D5" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E5" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D6" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E6" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D7" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E7" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D8" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E8" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D10" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E10" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,40 +656,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E11" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D12" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E12" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D13" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E13" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D14" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E14" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E15" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D16" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E16" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D17" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E17" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D18" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D19" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E19" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E20" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D21" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E21" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D22" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E22" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D23" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E23" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D24" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E24" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E25" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D26" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E26" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D27" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E27" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,40 +1013,40 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D28" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E28" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D29" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E29" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D31" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E31" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D32" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E32" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D33" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D34" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D35" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E35" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D36" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D37" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E37" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D38" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D39" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E39" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D40" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E40" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D41" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D42" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D43" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E43" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D44" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E44" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D45" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E45" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,40 +1391,40 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D46" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E46" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E47" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E48" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E49" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D50" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E50" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E51" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E52" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D53" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E53" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E54" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E55" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47.8</v>
+        <v>7.4</v>
       </c>
       <c r="D2" t="n">
-        <v>46.45</v>
+        <v>26.25</v>
       </c>
       <c r="E2" t="n">
-        <v>43.43</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13.8</v>
+        <v>24.8</v>
       </c>
       <c r="D3" t="n">
-        <v>26.55</v>
+        <v>33.2</v>
       </c>
       <c r="E3" t="n">
-        <v>28.69</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.4</v>
+        <v>23.2</v>
       </c>
       <c r="D4" t="n">
-        <v>26.25</v>
+        <v>31.25</v>
       </c>
       <c r="E4" t="n">
-        <v>30.86</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24.8</v>
+        <v>10.4</v>
       </c>
       <c r="D5" t="n">
-        <v>33.2</v>
+        <v>26.7</v>
       </c>
       <c r="E5" t="n">
-        <v>34.97</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.2</v>
+        <v>18.2</v>
       </c>
       <c r="D6" t="n">
-        <v>31.25</v>
+        <v>29.95</v>
       </c>
       <c r="E6" t="n">
-        <v>34.37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="E7" t="n">
-        <v>32.4</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95</v>
+        <v>24.55</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,61 +614,61 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="E9" t="n">
-        <v>32.14</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.6</v>
+        <v>14.2</v>
       </c>
       <c r="D10" t="n">
-        <v>24.55</v>
+        <v>30.53</v>
       </c>
       <c r="E10" t="n">
-        <v>30.51</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.199999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D11" t="n">
-        <v>29.4</v>
+        <v>36.67</v>
       </c>
       <c r="E11" t="n">
-        <v>33.54</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.2</v>
+        <v>25.2</v>
       </c>
       <c r="D12" t="n">
-        <v>30.53</v>
+        <v>40.07</v>
       </c>
       <c r="E12" t="n">
-        <v>35.33</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>36.67</v>
+        <v>41.67</v>
       </c>
       <c r="E13" t="n">
-        <v>39.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25.2</v>
+        <v>51.4</v>
       </c>
       <c r="D14" t="n">
-        <v>40.07</v>
+        <v>43.33</v>
       </c>
       <c r="E14" t="n">
-        <v>44.87</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="D15" t="n">
-        <v>41.67</v>
+        <v>47.87</v>
       </c>
       <c r="E15" t="n">
-        <v>46</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>51.4</v>
+        <v>34.6</v>
       </c>
       <c r="D16" t="n">
-        <v>43.33</v>
+        <v>56</v>
       </c>
       <c r="E16" t="n">
-        <v>45.5</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.2</v>
+        <v>39.4</v>
       </c>
       <c r="D17" t="n">
-        <v>47.87</v>
+        <v>57.27</v>
       </c>
       <c r="E17" t="n">
-        <v>49.63</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>61.73</v>
       </c>
       <c r="E18" t="n">
-        <v>55.67</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="D19" t="n">
-        <v>57.27</v>
+        <v>51.53</v>
       </c>
       <c r="E19" t="n">
-        <v>57.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>43.2</v>
       </c>
       <c r="D20" t="n">
-        <v>61.73</v>
+        <v>53.53</v>
       </c>
       <c r="E20" t="n">
-        <v>60.87</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38.6</v>
+        <v>44.6</v>
       </c>
       <c r="D21" t="n">
-        <v>51.53</v>
+        <v>57.93</v>
       </c>
       <c r="E21" t="n">
-        <v>51.73</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>43.2</v>
+        <v>48.8</v>
       </c>
       <c r="D22" t="n">
-        <v>53.53</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
-        <v>53.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="D23" t="n">
-        <v>57.93</v>
+        <v>58.33</v>
       </c>
       <c r="E23" t="n">
-        <v>55.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>63.4</v>
       </c>
       <c r="E24" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D25" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E25" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,61 +971,61 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D26" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E26" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D27" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E27" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D29" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E29" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D30" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E30" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D31" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D32" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1121,16 +1121,16 @@
         <v>49.2</v>
       </c>
       <c r="D33" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E33" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D34" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D35" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E35" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D36" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D37" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E37" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D38" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E38" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D39" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>40.4</v>
+        <v>50.4</v>
       </c>
       <c r="D40" t="n">
-        <v>61.1</v>
+        <v>71.5</v>
       </c>
       <c r="E40" t="n">
-        <v>56.48</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>45.6</v>
+        <v>47.4</v>
       </c>
       <c r="D41" t="n">
-        <v>71.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E41" t="n">
-        <v>62</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40.2</v>
+        <v>46.8</v>
       </c>
       <c r="D42" t="n">
-        <v>65.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="E42" t="n">
-        <v>59.52</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,82 +1328,82 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>50.4</v>
+        <v>27</v>
       </c>
       <c r="D43" t="n">
-        <v>71.5</v>
+        <v>56.5</v>
       </c>
       <c r="E43" t="n">
-        <v>61.32</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>47.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>70.5</v>
+        <v>61.1</v>
       </c>
       <c r="E44" t="n">
-        <v>60.68</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>46.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>67.5</v>
+        <v>60.6</v>
       </c>
       <c r="E45" t="n">
-        <v>58.08</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>27</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>56.5</v>
+        <v>59.45</v>
       </c>
       <c r="E46" t="n">
-        <v>52.96</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>90.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="D47" t="n">
-        <v>61.1</v>
+        <v>59.3</v>
       </c>
       <c r="E47" t="n">
-        <v>54.06</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>91.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>60.6</v>
+        <v>57.85</v>
       </c>
       <c r="E48" t="n">
-        <v>54.77</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>81.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>59.45</v>
+        <v>56.65</v>
       </c>
       <c r="E49" t="n">
-        <v>54.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>88.2</v>
+        <v>83</v>
       </c>
       <c r="D50" t="n">
-        <v>59.3</v>
+        <v>55.9</v>
       </c>
       <c r="E50" t="n">
-        <v>53.71</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>84.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>57.85</v>
+        <v>54</v>
       </c>
       <c r="E51" t="n">
-        <v>53.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,75 +1517,12 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>82.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>56.65</v>
+        <v>52.75</v>
       </c>
       <c r="E52" t="n">
-        <v>52.86</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>IC2605</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>83</v>
-      </c>
-      <c r="D53" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="E53" t="n">
-        <v>52.06</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>IC2605</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="D54" t="n">
-        <v>54</v>
-      </c>
-      <c r="E54" t="n">
-        <v>50.09</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>IC2605</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="D55" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="E55" t="n">
         <v>49.06</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="D2" t="n">
-        <v>26.25</v>
+        <v>33.2</v>
       </c>
       <c r="E2" t="n">
-        <v>30.86</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D3" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E3" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D4" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E4" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D5" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E5" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D7" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E7" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,40 +593,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E8" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D9" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E9" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D10" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E10" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D11" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E11" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E12" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D13" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D14" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E14" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D15" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E16" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E17" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D18" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E18" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D19" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E19" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D20" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E20" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D21" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E22" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D23" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E23" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D24" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E24" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,40 +950,40 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D25" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E25" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D26" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E26" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D28" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E28" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D29" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E29" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D30" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D31" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D32" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E32" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D33" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D34" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E34" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D35" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D36" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E36" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D37" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E37" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D38" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D39" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="40">

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.8</v>
+        <v>23.2</v>
       </c>
       <c r="D2" t="n">
-        <v>33.2</v>
+        <v>31.25</v>
       </c>
       <c r="E2" t="n">
-        <v>34.97</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D3" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E3" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D4" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E4" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D6" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E6" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,40 +572,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E7" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D8" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E8" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D9" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E9" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D10" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E10" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E11" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D12" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D13" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E13" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D14" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E15" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E16" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D17" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E17" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D18" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E18" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D19" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E19" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D20" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E20" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E21" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D22" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E22" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D23" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E23" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,40 +929,40 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D24" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E24" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D25" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E25" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D27" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E27" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D28" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E28" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D29" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D30" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D31" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E31" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D32" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D33" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E33" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D34" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D35" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E35" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D36" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E36" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D37" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D38" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D39" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E39" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D40" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E40" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D41" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E41" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,40 +1307,40 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D42" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E42" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E43" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E44" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E45" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D46" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E46" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E47" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E48" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D49" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E49" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E50" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E51" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D52" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E52" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="D2" t="n">
-        <v>31.25</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="n">
-        <v>34.37</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.4</v>
+        <v>18.2</v>
       </c>
       <c r="D3" t="n">
-        <v>26.7</v>
+        <v>29.95</v>
       </c>
       <c r="E3" t="n">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>29.95</v>
+        <v>26.8</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D5" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E5" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,40 +551,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E6" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D7" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E7" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D8" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E8" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D9" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E9" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E10" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D11" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D12" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E12" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D13" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E14" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D15" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E15" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D16" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E16" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D17" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E17" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D18" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E18" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D19" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E19" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E20" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E21" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D22" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E22" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,40 +908,40 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D23" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E23" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D24" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E24" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D26" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E26" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D27" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E27" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D28" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D29" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D30" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E30" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D31" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D32" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E32" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D33" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D34" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E34" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D35" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E35" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D36" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D37" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D38" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E38" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D39" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E39" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D40" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E40" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,40 +1286,40 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D41" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E41" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E42" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E43" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E44" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D45" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E45" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E46" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E47" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D48" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E48" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E49" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E50" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D51" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E51" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E52" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1526,6 +1526,27 @@
         <v>45.34</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IC2605</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="D53" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>46.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="E2" t="n">
-        <v>32.4</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D3" t="n">
-        <v>29.95</v>
+        <v>24.55</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,61 +509,61 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="E4" t="n">
-        <v>32.14</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.6</v>
+        <v>14.2</v>
       </c>
       <c r="D5" t="n">
-        <v>24.55</v>
+        <v>30.53</v>
       </c>
       <c r="E5" t="n">
-        <v>30.51</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.199999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="n">
-        <v>29.4</v>
+        <v>36.67</v>
       </c>
       <c r="E6" t="n">
-        <v>33.54</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14.2</v>
+        <v>25.2</v>
       </c>
       <c r="D7" t="n">
-        <v>30.53</v>
+        <v>40.07</v>
       </c>
       <c r="E7" t="n">
-        <v>35.33</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>36.67</v>
+        <v>41.67</v>
       </c>
       <c r="E8" t="n">
-        <v>39.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25.2</v>
+        <v>51.4</v>
       </c>
       <c r="D9" t="n">
-        <v>40.07</v>
+        <v>43.33</v>
       </c>
       <c r="E9" t="n">
-        <v>44.87</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="D10" t="n">
-        <v>41.67</v>
+        <v>47.87</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>51.4</v>
+        <v>34.6</v>
       </c>
       <c r="D11" t="n">
-        <v>43.33</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>45.5</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27.2</v>
+        <v>39.4</v>
       </c>
       <c r="D12" t="n">
-        <v>47.87</v>
+        <v>57.27</v>
       </c>
       <c r="E12" t="n">
-        <v>49.63</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>61.73</v>
       </c>
       <c r="E13" t="n">
-        <v>55.67</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="D14" t="n">
-        <v>57.27</v>
+        <v>51.53</v>
       </c>
       <c r="E14" t="n">
-        <v>57.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47</v>
+        <v>43.2</v>
       </c>
       <c r="D15" t="n">
-        <v>61.73</v>
+        <v>53.53</v>
       </c>
       <c r="E15" t="n">
-        <v>60.87</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38.6</v>
+        <v>44.6</v>
       </c>
       <c r="D16" t="n">
-        <v>51.53</v>
+        <v>57.93</v>
       </c>
       <c r="E16" t="n">
-        <v>51.73</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>43.2</v>
+        <v>48.8</v>
       </c>
       <c r="D17" t="n">
-        <v>53.53</v>
+        <v>61</v>
       </c>
       <c r="E17" t="n">
-        <v>53.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="D18" t="n">
-        <v>57.93</v>
+        <v>58.33</v>
       </c>
       <c r="E18" t="n">
-        <v>55.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>63.4</v>
       </c>
       <c r="E19" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E20" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,61 +866,61 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D21" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E21" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D22" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E22" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D24" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E24" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D25" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E25" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D26" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D27" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1016,16 +1016,16 @@
         <v>49.2</v>
       </c>
       <c r="D28" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E28" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D29" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D30" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E30" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D31" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D32" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E32" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D33" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E33" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D34" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D35" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>56.48</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
       <c r="D36" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E36" t="n">
-        <v>62</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>40.2</v>
+        <v>47.4</v>
       </c>
       <c r="D37" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E37" t="n">
-        <v>59.52</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50.4</v>
+        <v>46.8</v>
       </c>
       <c r="D38" t="n">
-        <v>71.5</v>
+        <v>67.5</v>
       </c>
       <c r="E38" t="n">
-        <v>61.32</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,61 +1244,61 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>47.4</v>
+        <v>27</v>
       </c>
       <c r="D39" t="n">
-        <v>70.5</v>
+        <v>56.5</v>
       </c>
       <c r="E39" t="n">
-        <v>60.68</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>46.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="E40" t="n">
-        <v>58.08</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>27</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>56.5</v>
+        <v>60.6</v>
       </c>
       <c r="E41" t="n">
-        <v>52.96</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>90.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>61.1</v>
+        <v>59.45</v>
       </c>
       <c r="E42" t="n">
-        <v>54.06</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>91.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D43" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E43" t="n">
-        <v>54.77</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
       <c r="E44" t="n">
-        <v>54.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>88.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>59.3</v>
+        <v>56.65</v>
       </c>
       <c r="E45" t="n">
-        <v>53.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>84.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D46" t="n">
-        <v>57.85</v>
+        <v>55.9</v>
       </c>
       <c r="E46" t="n">
-        <v>53.74</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E47" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E48" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D49" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E49" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E50" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E51" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,34 +1517,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D52" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E52" t="n">
-        <v>45.34</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>IC2605</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="D53" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="D2" t="n">
-        <v>26.8</v>
+        <v>24.55</v>
       </c>
       <c r="E2" t="n">
-        <v>32.14</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,40 +488,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E3" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D4" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E4" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D5" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E5" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D6" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E6" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E7" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D8" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D9" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E9" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D10" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E11" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E12" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D13" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E13" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D14" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E14" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D15" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E15" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D16" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E16" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E17" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E18" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E19" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,40 +845,40 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D20" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E20" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E21" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D23" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E23" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D24" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E24" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D25" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D26" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D27" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E27" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D28" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D29" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E29" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D30" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D31" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E31" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D32" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E32" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D33" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D34" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D35" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E35" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D36" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E36" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D37" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E37" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,40 +1223,40 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D38" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E38" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E39" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E40" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E41" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D42" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E42" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E43" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E44" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D45" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E45" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E46" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E47" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D48" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E48" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D49" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E49" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E50" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D51" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E51" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E52" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,40 +467,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>24.55</v>
+        <v>29.4</v>
       </c>
       <c r="E2" t="n">
-        <v>30.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D3" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E3" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D4" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E4" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D5" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E5" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E6" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D7" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D8" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E8" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D9" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E10" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E11" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D12" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E12" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D13" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E13" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D14" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E14" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D15" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E15" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E16" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D17" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E17" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E18" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,40 +824,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D19" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E19" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E20" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D22" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E22" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D23" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E23" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D24" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D25" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D26" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E26" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D27" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D28" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E28" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D29" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D30" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E30" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D31" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E31" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D32" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D33" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D34" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E34" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D35" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E35" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D36" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E36" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D37" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E37" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E38" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E39" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E40" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D41" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E41" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E42" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E43" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D44" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E44" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E45" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E46" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D47" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E47" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D48" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E48" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E49" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D50" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E50" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E51" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D52" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,28 +458,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IC2602</t>
+          <t>IC2603</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D2" t="n">
-        <v>29.4</v>
+        <v>30.53</v>
       </c>
       <c r="E2" t="n">
-        <v>33.54</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14.2</v>
+        <v>22.4</v>
       </c>
       <c r="D3" t="n">
-        <v>30.53</v>
+        <v>36.67</v>
       </c>
       <c r="E3" t="n">
-        <v>35.33</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D4" t="n">
-        <v>36.67</v>
+        <v>40.07</v>
       </c>
       <c r="E4" t="n">
-        <v>39.87</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>40.07</v>
+        <v>41.67</v>
       </c>
       <c r="E5" t="n">
-        <v>44.87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
       <c r="D6" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.4</v>
+        <v>27.2</v>
       </c>
       <c r="D7" t="n">
-        <v>43.33</v>
+        <v>47.87</v>
       </c>
       <c r="E7" t="n">
-        <v>45.5</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D8" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E9" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D10" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E10" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D11" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E11" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D12" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E12" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D13" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E13" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D14" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E15" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E16" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D17" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E17" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,40 +803,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D18" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E18" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E19" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D21" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E21" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D22" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E22" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D23" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D24" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D25" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E25" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D26" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D27" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E27" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D28" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D29" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E29" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D30" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E30" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D31" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D32" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D33" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E33" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D34" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E34" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D35" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E35" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,40 +1181,40 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D36" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E36" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E37" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E38" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E39" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D40" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E40" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E41" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E42" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D43" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E43" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E44" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E45" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D46" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E46" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D47" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E47" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E48" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D49" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E49" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E50" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D51" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E52" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1526,6 +1526,27 @@
         <v>50.09</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="D53" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="E53" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,27 @@
         <v>47.8</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>49.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,6 +1568,27 @@
         <v>49.17</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="E55" t="n">
+        <v>52.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,27 @@
         <v>52.37</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="D56" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="E56" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1610,6 +1610,27 @@
         <v>51.8</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>52.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,6 +1631,27 @@
         <v>52.93</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>59.27</v>
+      </c>
+      <c r="E58" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14.2</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>30.53</v>
+        <v>41.67</v>
       </c>
       <c r="E2" t="n">
-        <v>35.33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.4</v>
+        <v>51.4</v>
       </c>
       <c r="D3" t="n">
-        <v>36.67</v>
+        <v>43.33</v>
       </c>
       <c r="E3" t="n">
-        <v>39.87</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.2</v>
+        <v>27.2</v>
       </c>
       <c r="D4" t="n">
-        <v>40.07</v>
+        <v>47.87</v>
       </c>
       <c r="E4" t="n">
-        <v>44.87</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>34.6</v>
       </c>
       <c r="D5" t="n">
-        <v>41.67</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>51.4</v>
+        <v>39.4</v>
       </c>
       <c r="D6" t="n">
-        <v>43.33</v>
+        <v>57.27</v>
       </c>
       <c r="E6" t="n">
-        <v>45.5</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.2</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
-        <v>47.87</v>
+        <v>61.73</v>
       </c>
       <c r="E7" t="n">
-        <v>49.63</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>34.6</v>
+        <v>38.6</v>
       </c>
       <c r="D8" t="n">
-        <v>56</v>
+        <v>51.53</v>
       </c>
       <c r="E8" t="n">
-        <v>55.67</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39.4</v>
+        <v>43.2</v>
       </c>
       <c r="D9" t="n">
-        <v>57.27</v>
+        <v>53.53</v>
       </c>
       <c r="E9" t="n">
-        <v>57.47</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47</v>
+        <v>44.6</v>
       </c>
       <c r="D10" t="n">
-        <v>61.73</v>
+        <v>57.93</v>
       </c>
       <c r="E10" t="n">
-        <v>60.87</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.6</v>
+        <v>48.8</v>
       </c>
       <c r="D11" t="n">
-        <v>51.53</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>51.73</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>43.2</v>
+        <v>41.6</v>
       </c>
       <c r="D12" t="n">
-        <v>53.53</v>
+        <v>58.33</v>
       </c>
       <c r="E12" t="n">
-        <v>53.6</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>44.6</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>57.93</v>
+        <v>63.4</v>
       </c>
       <c r="E13" t="n">
-        <v>55.2</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>48.8</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>67.2</v>
       </c>
       <c r="E14" t="n">
-        <v>58.4</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,82 +740,82 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>41.6</v>
+        <v>64.2</v>
       </c>
       <c r="D15" t="n">
-        <v>58.33</v>
+        <v>71.8</v>
       </c>
       <c r="E15" t="n">
-        <v>56.6</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>63.4</v>
+        <v>76.3</v>
       </c>
       <c r="E16" t="n">
-        <v>61.3</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>55</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>67.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>61.97</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>64.2</v>
+        <v>55.6</v>
       </c>
       <c r="D18" t="n">
-        <v>71.8</v>
+        <v>77.8</v>
       </c>
       <c r="E18" t="n">
-        <v>65.37</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>53.6</v>
       </c>
       <c r="D19" t="n">
-        <v>76.3</v>
+        <v>78.7</v>
       </c>
       <c r="E19" t="n">
-        <v>67.72</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>70.59999999999999</v>
+        <v>49.2</v>
       </c>
       <c r="D20" t="n">
-        <v>72.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>63.08</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.6</v>
+        <v>52.2</v>
       </c>
       <c r="D21" t="n">
-        <v>77.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>66.12</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D22" t="n">
-        <v>78.7</v>
+        <v>75.3</v>
       </c>
       <c r="E22" t="n">
-        <v>66.2</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D23" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>63.24</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>52.2</v>
+        <v>55.2</v>
       </c>
       <c r="D24" t="n">
-        <v>73.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E24" t="n">
-        <v>63.92</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>49.2</v>
+        <v>57.4</v>
       </c>
       <c r="D25" t="n">
-        <v>75.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>64.04000000000001</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>46.4</v>
+        <v>49.4</v>
       </c>
       <c r="D26" t="n">
-        <v>72.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E26" t="n">
-        <v>61.4</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>55.2</v>
+        <v>40.4</v>
       </c>
       <c r="D27" t="n">
-        <v>78.8</v>
+        <v>61.1</v>
       </c>
       <c r="E27" t="n">
-        <v>65.59999999999999</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>57.4</v>
+        <v>45.6</v>
       </c>
       <c r="D28" t="n">
-        <v>78.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>65.76000000000001</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>49.4</v>
+        <v>40.2</v>
       </c>
       <c r="D29" t="n">
-        <v>73.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>63.64</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40.4</v>
+        <v>50.4</v>
       </c>
       <c r="D30" t="n">
-        <v>61.1</v>
+        <v>71.5</v>
       </c>
       <c r="E30" t="n">
-        <v>56.48</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>45.6</v>
+        <v>47.4</v>
       </c>
       <c r="D31" t="n">
-        <v>71.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E31" t="n">
-        <v>62</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>40.2</v>
+        <v>46.8</v>
       </c>
       <c r="D32" t="n">
-        <v>65.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="E32" t="n">
-        <v>59.52</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,82 +1118,82 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50.4</v>
+        <v>27</v>
       </c>
       <c r="D33" t="n">
-        <v>71.5</v>
+        <v>56.5</v>
       </c>
       <c r="E33" t="n">
-        <v>61.32</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>47.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>70.5</v>
+        <v>61.1</v>
       </c>
       <c r="E34" t="n">
-        <v>60.68</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>46.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>67.5</v>
+        <v>60.6</v>
       </c>
       <c r="E35" t="n">
-        <v>58.08</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>27</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>56.5</v>
+        <v>59.45</v>
       </c>
       <c r="E36" t="n">
-        <v>52.96</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>90.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="D37" t="n">
-        <v>61.1</v>
+        <v>59.3</v>
       </c>
       <c r="E37" t="n">
-        <v>54.06</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>91.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>60.6</v>
+        <v>57.85</v>
       </c>
       <c r="E38" t="n">
-        <v>54.77</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>81.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>59.45</v>
+        <v>56.65</v>
       </c>
       <c r="E39" t="n">
-        <v>54.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>88.2</v>
+        <v>83</v>
       </c>
       <c r="D40" t="n">
-        <v>59.3</v>
+        <v>55.9</v>
       </c>
       <c r="E40" t="n">
-        <v>53.71</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>84.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>57.85</v>
+        <v>54</v>
       </c>
       <c r="E41" t="n">
-        <v>53.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>82.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>56.65</v>
+        <v>52.75</v>
       </c>
       <c r="E42" t="n">
-        <v>52.86</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>83</v>
+        <v>72.8</v>
       </c>
       <c r="D43" t="n">
-        <v>55.9</v>
+        <v>50.8</v>
       </c>
       <c r="E43" t="n">
-        <v>52.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>74.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>54</v>
+        <v>48.7</v>
       </c>
       <c r="E44" t="n">
-        <v>50.09</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>72.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>52.75</v>
+        <v>49.2</v>
       </c>
       <c r="E45" t="n">
-        <v>49.06</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>72.8</v>
+        <v>74.8</v>
       </c>
       <c r="D46" t="n">
-        <v>50.8</v>
+        <v>53.5</v>
       </c>
       <c r="E46" t="n">
-        <v>47.49</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>64</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>48.7</v>
+        <v>54.75</v>
       </c>
       <c r="E47" t="n">
-        <v>45.34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>66.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="D48" t="n">
-        <v>49.2</v>
+        <v>52.6</v>
       </c>
       <c r="E48" t="n">
-        <v>46.11</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,82 +1454,82 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>74.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>53.5</v>
+        <v>55</v>
       </c>
       <c r="E49" t="n">
-        <v>49.69</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>79.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D50" t="n">
-        <v>54.75</v>
+        <v>49.07</v>
       </c>
       <c r="E50" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>70.2</v>
+        <v>50.6</v>
       </c>
       <c r="D51" t="n">
-        <v>52.6</v>
+        <v>50.4</v>
       </c>
       <c r="E51" t="n">
-        <v>48.74</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>80.59999999999999</v>
+        <v>59.4</v>
       </c>
       <c r="D52" t="n">
-        <v>55</v>
+        <v>57.13</v>
       </c>
       <c r="E52" t="n">
-        <v>50.09</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>50.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>49.07</v>
+        <v>53.33</v>
       </c>
       <c r="E53" t="n">
-        <v>47.8</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>50.6</v>
+        <v>57.2</v>
       </c>
       <c r="D54" t="n">
-        <v>50.4</v>
+        <v>54.6</v>
       </c>
       <c r="E54" t="n">
-        <v>49.17</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>59.4</v>
+        <v>57.4</v>
       </c>
       <c r="D55" t="n">
-        <v>57.13</v>
+        <v>59.27</v>
       </c>
       <c r="E55" t="n">
-        <v>52.37</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>66.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="D56" t="n">
-        <v>53.33</v>
+        <v>60.8</v>
       </c>
       <c r="E56" t="n">
-        <v>51.8</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>57.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>54.6</v>
+        <v>59.73</v>
       </c>
       <c r="E57" t="n">
-        <v>52.93</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>57.4</v>
+        <v>56.4</v>
       </c>
       <c r="D58" t="n">
-        <v>59.27</v>
+        <v>61.4</v>
       </c>
       <c r="E58" t="n">
-        <v>55.2</v>
+        <v>58.53</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,27 @@
         <v>58.53</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>67</v>
+      </c>
+      <c r="D59" t="n">
+        <v>63.53</v>
+      </c>
+      <c r="E59" t="n">
+        <v>60.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="D2" t="n">
-        <v>41.67</v>
+        <v>47.87</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>51.4</v>
+        <v>34.6</v>
       </c>
       <c r="D3" t="n">
-        <v>43.33</v>
+        <v>56</v>
       </c>
       <c r="E3" t="n">
-        <v>45.5</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27.2</v>
+        <v>39.4</v>
       </c>
       <c r="D4" t="n">
-        <v>47.87</v>
+        <v>57.27</v>
       </c>
       <c r="E4" t="n">
-        <v>49.63</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>61.73</v>
       </c>
       <c r="E5" t="n">
-        <v>55.67</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39.4</v>
+        <v>38.6</v>
       </c>
       <c r="D6" t="n">
-        <v>57.27</v>
+        <v>51.53</v>
       </c>
       <c r="E6" t="n">
-        <v>57.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>43.2</v>
       </c>
       <c r="D7" t="n">
-        <v>61.73</v>
+        <v>53.53</v>
       </c>
       <c r="E7" t="n">
-        <v>60.87</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38.6</v>
+        <v>44.6</v>
       </c>
       <c r="D8" t="n">
-        <v>51.53</v>
+        <v>57.93</v>
       </c>
       <c r="E8" t="n">
-        <v>51.73</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>43.2</v>
+        <v>48.8</v>
       </c>
       <c r="D9" t="n">
-        <v>53.53</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>53.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="D10" t="n">
-        <v>57.93</v>
+        <v>58.33</v>
       </c>
       <c r="E10" t="n">
-        <v>55.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>63.4</v>
       </c>
       <c r="E11" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E12" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,61 +698,61 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D13" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E13" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E14" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D16" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E16" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D17" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E17" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D18" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D19" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -848,16 +848,16 @@
         <v>49.2</v>
       </c>
       <c r="D20" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E20" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D21" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D22" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E22" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D23" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D24" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E24" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D25" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E25" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D26" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D27" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>56.48</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
       <c r="D28" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E28" t="n">
-        <v>62</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>40.2</v>
+        <v>47.4</v>
       </c>
       <c r="D29" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E29" t="n">
-        <v>59.52</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>50.4</v>
+        <v>46.8</v>
       </c>
       <c r="D30" t="n">
-        <v>71.5</v>
+        <v>67.5</v>
       </c>
       <c r="E30" t="n">
-        <v>61.32</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,61 +1076,61 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>47.4</v>
+        <v>27</v>
       </c>
       <c r="D31" t="n">
-        <v>70.5</v>
+        <v>56.5</v>
       </c>
       <c r="E31" t="n">
-        <v>60.68</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>46.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="E32" t="n">
-        <v>58.08</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>56.5</v>
+        <v>60.6</v>
       </c>
       <c r="E33" t="n">
-        <v>52.96</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>90.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>61.1</v>
+        <v>59.45</v>
       </c>
       <c r="E34" t="n">
-        <v>54.06</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>91.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D35" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E35" t="n">
-        <v>54.77</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
       <c r="E36" t="n">
-        <v>54.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>88.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>59.3</v>
+        <v>56.65</v>
       </c>
       <c r="E37" t="n">
-        <v>53.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>84.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D38" t="n">
-        <v>57.85</v>
+        <v>55.9</v>
       </c>
       <c r="E38" t="n">
-        <v>53.74</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E39" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E40" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D41" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E41" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E42" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E43" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D44" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E44" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E45" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D46" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E46" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,61 +1412,61 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D48" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E48" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D49" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E49" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D50" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E50" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E51" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D52" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E52" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D53" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E53" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D54" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E54" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E55" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D56" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E56" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D57" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E57" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,34 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D58" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E58" t="n">
-        <v>58.53</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>IC2606</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>67</v>
-      </c>
-      <c r="D59" t="n">
-        <v>63.53</v>
-      </c>
-      <c r="E59" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.2</v>
+        <v>34.6</v>
       </c>
       <c r="D2" t="n">
-        <v>47.87</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
-        <v>49.63</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E3" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D4" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E4" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D5" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E5" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D6" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E6" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D7" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E7" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D8" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E9" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D10" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E10" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E11" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,40 +677,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D12" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E12" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E13" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D15" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E15" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D16" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E16" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D17" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D18" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D19" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E19" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D20" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D21" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E21" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D22" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D23" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E23" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D24" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E24" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D25" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D26" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D27" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E27" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D28" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E28" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D29" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E29" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,40 +1055,40 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D30" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E30" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E31" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E32" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E33" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D34" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E34" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E35" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E36" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D37" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E37" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E38" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E39" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D40" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E40" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E41" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E42" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D43" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E43" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E44" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D45" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E45" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,40 +1391,40 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E46" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D47" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E47" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D48" t="n">
         <v>50.4</v>
       </c>
-      <c r="D48" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E48" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D49" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E49" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E50" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D51" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E51" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D52" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E52" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D53" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E53" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E54" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D55" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E55" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D56" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E56" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D57" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E57" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D58" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E58" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34.6</v>
+        <v>39.4</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>57.27</v>
       </c>
       <c r="E2" t="n">
-        <v>55.67</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D3" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E3" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D4" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E4" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D5" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E5" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D6" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E6" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D7" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E8" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E9" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E10" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,40 +656,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D11" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E11" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E12" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D14" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E14" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D15" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E15" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D16" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D17" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D18" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E18" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D19" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D20" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E20" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D21" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D22" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E22" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D23" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E23" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D24" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D25" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D26" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E26" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D27" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E27" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D28" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E28" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,40 +1034,40 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E29" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E30" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E31" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E32" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D33" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E33" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E34" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E35" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D36" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E36" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E37" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E38" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D39" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E39" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E40" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E41" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D42" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E42" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E43" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D44" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E44" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,40 +1370,40 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E45" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D46" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E46" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D47" t="n">
         <v>50.4</v>
       </c>
-      <c r="D47" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E47" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D48" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E48" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E49" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D50" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E50" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D51" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E51" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D52" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E52" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E53" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D54" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E54" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D55" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E55" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D56" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E56" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D57" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E57" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D58" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E58" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>57.27</v>
+        <v>61.73</v>
       </c>
       <c r="E2" t="n">
-        <v>57.47</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>38.6</v>
       </c>
       <c r="D3" t="n">
-        <v>61.73</v>
+        <v>51.53</v>
       </c>
       <c r="E3" t="n">
-        <v>60.87</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.6</v>
+        <v>43.2</v>
       </c>
       <c r="D4" t="n">
-        <v>51.53</v>
+        <v>53.53</v>
       </c>
       <c r="E4" t="n">
-        <v>51.73</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D5" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E5" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D6" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E7" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E8" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E9" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,40 +635,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D10" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E10" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E11" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D13" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E13" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D14" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E14" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D15" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D16" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D17" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E17" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D18" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D19" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E19" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D20" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D21" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E21" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D22" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E22" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D23" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D24" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D25" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E25" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D26" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E26" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D27" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E27" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,40 +1013,40 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E28" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E29" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E30" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E31" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D32" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E32" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E33" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E34" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D35" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E35" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E36" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E37" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D38" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E38" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D39" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E39" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E40" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D41" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E41" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E42" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D43" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,40 +1349,40 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E44" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D45" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E45" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D46" t="n">
         <v>50.4</v>
       </c>
-      <c r="D46" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E46" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D47" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E47" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E48" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D49" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E49" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D50" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E50" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D51" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E51" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E52" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D53" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E53" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D54" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E54" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D55" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E55" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D56" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E56" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D57" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E57" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D58" t="n">
         <v>60.13</v>
       </c>
       <c r="E58" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,27 @@
         <v>58.03</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>63.27</v>
+      </c>
+      <c r="E59" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>43.2</v>
       </c>
       <c r="D2" t="n">
-        <v>61.73</v>
+        <v>53.53</v>
       </c>
       <c r="E2" t="n">
-        <v>60.87</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38.6</v>
+        <v>44.6</v>
       </c>
       <c r="D3" t="n">
-        <v>51.53</v>
+        <v>57.93</v>
       </c>
       <c r="E3" t="n">
-        <v>51.73</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43.2</v>
+        <v>48.8</v>
       </c>
       <c r="D4" t="n">
-        <v>53.53</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>53.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="D5" t="n">
-        <v>57.93</v>
+        <v>58.33</v>
       </c>
       <c r="E5" t="n">
-        <v>55.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>63.4</v>
       </c>
       <c r="E6" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E7" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,61 +593,61 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D8" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E8" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E9" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D11" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E11" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D12" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E12" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D13" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D14" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -743,16 +743,16 @@
         <v>49.2</v>
       </c>
       <c r="D15" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E15" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D16" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D17" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E17" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D18" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D19" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E19" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D20" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E20" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D21" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D22" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>56.48</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
       <c r="D23" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E23" t="n">
-        <v>62</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40.2</v>
+        <v>47.4</v>
       </c>
       <c r="D24" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E24" t="n">
-        <v>59.52</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50.4</v>
+        <v>46.8</v>
       </c>
       <c r="D25" t="n">
-        <v>71.5</v>
+        <v>67.5</v>
       </c>
       <c r="E25" t="n">
-        <v>61.32</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,61 +971,61 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>47.4</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>70.5</v>
+        <v>56.5</v>
       </c>
       <c r="E26" t="n">
-        <v>60.68</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>46.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="E27" t="n">
-        <v>58.08</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>56.5</v>
+        <v>60.6</v>
       </c>
       <c r="E28" t="n">
-        <v>52.96</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>90.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>61.1</v>
+        <v>59.45</v>
       </c>
       <c r="E29" t="n">
-        <v>54.06</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>91.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D30" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E30" t="n">
-        <v>54.77</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
       <c r="E31" t="n">
-        <v>54.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>88.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>59.3</v>
+        <v>56.65</v>
       </c>
       <c r="E32" t="n">
-        <v>53.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>84.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D33" t="n">
-        <v>57.85</v>
+        <v>55.9</v>
       </c>
       <c r="E33" t="n">
-        <v>53.74</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E34" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E35" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D36" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E36" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E37" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E38" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D39" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E39" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E40" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D41" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E41" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,61 +1307,61 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E42" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D43" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E43" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E44" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D45" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E45" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E46" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D47" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E47" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D48" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E48" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D49" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E49" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E50" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D51" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E51" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D52" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E52" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D53" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E53" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D54" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E54" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D55" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E55" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D56" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E56" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D57" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E57" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,34 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D58" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E58" t="n">
-        <v>58.03</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>IC2606</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="D59" t="n">
-        <v>63.27</v>
-      </c>
-      <c r="E59" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="D2" t="n">
-        <v>53.53</v>
+        <v>57.93</v>
       </c>
       <c r="E2" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D3" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E4" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E5" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D6" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E6" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,40 +572,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D7" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E7" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E8" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D10" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E10" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D11" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E11" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D12" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D13" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D14" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E14" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D15" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D16" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E16" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D17" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D18" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E18" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D19" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E19" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D20" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D21" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D22" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E22" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D23" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E23" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D24" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E24" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,40 +950,40 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E25" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E26" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E27" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E28" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D29" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E29" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E30" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E31" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D32" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E32" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E33" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E34" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D35" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E35" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E36" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E37" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D38" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E38" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E39" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D40" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E40" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,40 +1286,40 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E41" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D42" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E42" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D43" t="n">
         <v>50.4</v>
       </c>
-      <c r="D43" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E43" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D44" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E44" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E45" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D46" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E46" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D47" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E47" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D48" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E48" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E49" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D50" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E50" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D51" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E51" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D52" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E52" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D53" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E53" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D54" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E54" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D55" t="n">
         <v>60.13</v>
       </c>
       <c r="E55" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D56" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E56" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D57" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E57" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E58" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>44.6</v>
+        <v>48.8</v>
       </c>
       <c r="D2" t="n">
-        <v>57.93</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E3" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E4" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D5" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E5" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,40 +551,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D6" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E6" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E7" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D9" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E9" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D10" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E10" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D11" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D12" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D13" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E13" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D14" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D15" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E15" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D16" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D17" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E17" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D18" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E18" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D19" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D20" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D21" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E21" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D22" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E22" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D23" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E23" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,40 +929,40 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D24" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E24" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E25" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E26" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E27" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D28" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E28" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E29" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E30" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D31" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E31" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E32" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E33" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D34" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E34" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D35" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E35" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E36" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D37" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E37" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E38" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D39" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,40 +1265,40 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E40" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D41" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E41" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D42" t="n">
         <v>50.4</v>
       </c>
-      <c r="D42" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E42" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D43" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E43" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E44" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D45" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E45" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D46" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E46" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D47" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E47" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E48" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D49" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E49" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D50" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E50" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D51" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E51" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D52" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E52" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D53" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E53" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D54" t="n">
         <v>60.13</v>
       </c>
       <c r="E54" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D55" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E55" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D56" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E56" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E57" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D58" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E58" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>58.33</v>
       </c>
       <c r="E2" t="n">
-        <v>58.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41.6</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>58.33</v>
+        <v>63.4</v>
       </c>
       <c r="E3" t="n">
-        <v>56.6</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="E4" t="n">
-        <v>61.3</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,40 +530,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D5" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E5" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E6" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D8" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E8" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D9" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E9" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D10" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D11" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D12" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E12" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D13" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D14" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E14" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D15" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D16" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E16" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D17" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E17" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D18" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D19" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D20" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E20" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D21" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E21" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D22" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E22" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,40 +908,40 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D23" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E23" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E24" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E25" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E26" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D27" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E27" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E28" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E29" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D30" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E30" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E32" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D33" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E33" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D34" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E34" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E35" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D36" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E36" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E37" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D38" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E38" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,40 +1244,40 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E39" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D40" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E40" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D41" t="n">
         <v>50.4</v>
       </c>
-      <c r="D41" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E41" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D42" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E42" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E43" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D44" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E44" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D45" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E45" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D46" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E46" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E47" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D48" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E48" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D49" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E49" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D50" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E50" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D51" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E51" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D52" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E52" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D53" t="n">
         <v>60.13</v>
       </c>
       <c r="E53" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D54" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E54" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D55" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E55" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E56" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D57" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E57" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E58" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,27 @@
         <v>61.77</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>66</v>
+      </c>
+      <c r="D59" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>61.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41.6</v>
+        <v>55</v>
       </c>
       <c r="D2" t="n">
-        <v>58.33</v>
+        <v>67.2</v>
       </c>
       <c r="E2" t="n">
-        <v>56.6</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>64.2</v>
       </c>
       <c r="D3" t="n">
-        <v>63.4</v>
+        <v>71.8</v>
       </c>
       <c r="E3" t="n">
-        <v>61.3</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>67.2</v>
+        <v>76.3</v>
       </c>
       <c r="E4" t="n">
-        <v>61.97</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>65.37</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D6" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E6" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D7" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E7" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D8" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D9" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -638,16 +638,16 @@
         <v>49.2</v>
       </c>
       <c r="D10" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E10" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D11" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D12" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E12" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D13" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D14" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E14" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D15" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E15" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D16" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D17" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>56.48</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
       <c r="D18" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E18" t="n">
-        <v>62</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40.2</v>
+        <v>47.4</v>
       </c>
       <c r="D19" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E19" t="n">
-        <v>59.52</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>50.4</v>
+        <v>46.8</v>
       </c>
       <c r="D20" t="n">
-        <v>71.5</v>
+        <v>67.5</v>
       </c>
       <c r="E20" t="n">
-        <v>61.32</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,61 +866,61 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>47.4</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>70.5</v>
+        <v>56.5</v>
       </c>
       <c r="E21" t="n">
-        <v>60.68</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>46.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="E22" t="n">
-        <v>58.08</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>56.5</v>
+        <v>60.6</v>
       </c>
       <c r="E23" t="n">
-        <v>52.96</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>90.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>61.1</v>
+        <v>59.45</v>
       </c>
       <c r="E24" t="n">
-        <v>54.06</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>91.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D25" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E25" t="n">
-        <v>54.77</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
       <c r="E26" t="n">
-        <v>54.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>88.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>59.3</v>
+        <v>56.65</v>
       </c>
       <c r="E27" t="n">
-        <v>53.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>84.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D28" t="n">
-        <v>57.85</v>
+        <v>55.9</v>
       </c>
       <c r="E28" t="n">
-        <v>53.74</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E29" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E30" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E31" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E32" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E33" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D34" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E34" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E35" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D36" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E36" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,61 +1202,61 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D38" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E38" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D39" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E39" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D40" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E40" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E41" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D42" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E42" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D43" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E43" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D44" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E44" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E45" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D46" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E46" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D47" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E47" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D48" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E48" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D49" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E49" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D50" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E50" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D51" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E51" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D52" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E52" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D53" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E53" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E54" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D55" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E55" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E56" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D57" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E57" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,34 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D58" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E58" t="n">
-        <v>61.77</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>IC2606</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>66</v>
-      </c>
-      <c r="D59" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="E59" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,40 +467,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>64.2</v>
       </c>
       <c r="D2" t="n">
-        <v>67.2</v>
+        <v>71.8</v>
       </c>
       <c r="E2" t="n">
-        <v>61.97</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E3" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D5" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E5" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D6" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E6" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D7" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D8" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D9" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E9" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D10" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D11" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E11" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D12" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D13" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E13" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D14" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E14" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D15" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D16" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D17" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E17" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D18" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E18" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D19" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E19" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,40 +845,40 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E20" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E21" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E22" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E23" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D24" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E24" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E25" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E26" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D27" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E27" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E29" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D30" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E30" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D31" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E31" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E32" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D33" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E33" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E34" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D35" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E35" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,40 +1181,40 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E36" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D37" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E37" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D38" t="n">
         <v>50.4</v>
       </c>
-      <c r="D38" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E38" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D39" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E39" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E40" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D41" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E41" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D42" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E42" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D43" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E43" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E44" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D45" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E45" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D46" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E46" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D47" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E47" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D48" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E48" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D49" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E49" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D50" t="n">
         <v>60.13</v>
       </c>
       <c r="E50" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D51" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E51" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D52" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E52" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E53" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D54" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E54" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E55" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D56" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E56" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D57" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E57" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D58" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,28 +458,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IC2603</t>
+          <t>IC2604</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64.2</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>71.8</v>
+        <v>76.3</v>
       </c>
       <c r="E2" t="n">
-        <v>65.37</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>67.72</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="D4" t="n">
-        <v>72.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E4" t="n">
-        <v>63.08</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D5" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E5" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D6" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D7" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D8" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E8" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D9" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D10" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E10" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D11" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D12" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E12" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D13" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E13" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D14" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D15" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D16" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E16" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D17" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E17" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D18" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E18" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,40 +824,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E19" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E20" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E21" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E22" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D23" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E23" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E24" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E25" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D26" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E26" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E27" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E28" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D29" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E29" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E30" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E31" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D32" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E32" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E33" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D34" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E34" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,40 +1160,40 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E35" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E36" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D37" t="n">
         <v>50.4</v>
       </c>
-      <c r="D37" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E37" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D38" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E38" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E39" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D40" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E40" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D41" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E41" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D42" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E42" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E43" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D44" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E44" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D45" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E45" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D46" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E46" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D47" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E47" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D48" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E48" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D49" t="n">
         <v>60.13</v>
       </c>
       <c r="E49" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D50" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E50" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D51" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E51" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E52" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D53" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E53" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E54" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D55" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E55" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D56" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E56" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D58" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E58" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,27 @@
         <v>61</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IC2606</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="E59" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D2" t="n">
-        <v>76.3</v>
+        <v>77.8</v>
       </c>
       <c r="E2" t="n">
-        <v>67.72</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>70.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D3" t="n">
-        <v>72.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E3" t="n">
-        <v>63.08</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>55.6</v>
+        <v>49.2</v>
       </c>
       <c r="D4" t="n">
-        <v>77.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>66.12</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53.6</v>
+        <v>52.2</v>
       </c>
       <c r="D5" t="n">
-        <v>78.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>66.2</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -554,16 +554,16 @@
         <v>49.2</v>
       </c>
       <c r="D6" t="n">
-        <v>71.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E6" t="n">
-        <v>63.24</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D7" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D8" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E8" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D9" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D10" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E10" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D11" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E11" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D12" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D13" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>56.48</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
       <c r="D14" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>40.2</v>
+        <v>47.4</v>
       </c>
       <c r="D15" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E15" t="n">
-        <v>59.52</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>50.4</v>
+        <v>46.8</v>
       </c>
       <c r="D16" t="n">
-        <v>71.5</v>
+        <v>67.5</v>
       </c>
       <c r="E16" t="n">
-        <v>61.32</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,61 +782,61 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47.4</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
-        <v>70.5</v>
+        <v>56.5</v>
       </c>
       <c r="E17" t="n">
-        <v>60.68</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>46.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="E18" t="n">
-        <v>58.08</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>56.5</v>
+        <v>60.6</v>
       </c>
       <c r="E19" t="n">
-        <v>52.96</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>90.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>61.1</v>
+        <v>59.45</v>
       </c>
       <c r="E20" t="n">
-        <v>54.06</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>91.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D21" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E21" t="n">
-        <v>54.77</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
       <c r="E22" t="n">
-        <v>54.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>88.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>59.3</v>
+        <v>56.65</v>
       </c>
       <c r="E23" t="n">
-        <v>53.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>84.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D24" t="n">
-        <v>57.85</v>
+        <v>55.9</v>
       </c>
       <c r="E24" t="n">
-        <v>53.74</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E25" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E26" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E27" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E28" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E29" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D30" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E30" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E31" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D32" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E32" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,61 +1118,61 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D34" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E34" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D35" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E35" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D36" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E36" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E37" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D38" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E38" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D39" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E39" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D40" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E40" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E41" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D42" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E42" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D43" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E43" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D44" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E44" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D45" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E45" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D46" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E46" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D47" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E47" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D48" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E48" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D49" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E49" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E50" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D51" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E51" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E52" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D53" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E53" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D54" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E54" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D55" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D56" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E56" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,54 +1622,12 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D57" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E57" t="n">
-        <v>62.97</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>IC2606</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="D58" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="E58" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>IC2606</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="D59" t="n">
-        <v>55.13</v>
-      </c>
-      <c r="E59" t="n">
         <v>56.9</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.6</v>
+        <v>53.6</v>
       </c>
       <c r="D2" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="E2" t="n">
-        <v>66.12</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D3" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D4" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D5" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E5" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D6" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D7" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E7" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D8" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D9" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E9" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D10" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E10" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D11" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D12" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D13" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E13" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D14" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E14" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D15" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E15" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,40 +761,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E16" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E17" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E18" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E19" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D20" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E20" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E21" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E22" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D23" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E23" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E24" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E25" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D26" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E26" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E27" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E28" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D29" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E29" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E30" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D31" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E31" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,40 +1097,40 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E32" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D33" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E33" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D34" t="n">
         <v>50.4</v>
       </c>
-      <c r="D34" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E34" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D35" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E35" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E36" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D37" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E37" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D38" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E38" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D39" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E39" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E40" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D41" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E41" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D42" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E42" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D43" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E43" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D44" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E44" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D45" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E45" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D46" t="n">
         <v>60.13</v>
       </c>
       <c r="E46" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D47" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E47" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D48" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E48" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E49" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D50" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E50" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E51" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D52" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E52" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D53" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E53" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D54" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D55" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E55" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,34 +1601,34 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D56" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D57" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E57" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53.6</v>
+        <v>49.2</v>
       </c>
       <c r="D2" t="n">
-        <v>78.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>66.2</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D3" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D4" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E4" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D5" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D6" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E6" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D7" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D8" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E8" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D9" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E9" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D10" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D11" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D12" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E12" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D13" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E13" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D14" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E14" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,40 +740,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E15" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E16" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E17" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E18" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D19" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E19" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E20" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E21" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D22" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E22" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E24" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D25" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E25" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D26" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E26" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E27" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D28" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E28" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E29" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D30" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,40 +1076,40 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E31" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E32" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D33" t="n">
         <v>50.4</v>
       </c>
-      <c r="D33" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E33" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D34" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E34" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E35" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D36" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E36" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D37" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E37" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D38" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E38" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E39" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D40" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E40" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D41" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E41" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D42" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E42" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D43" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E43" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D44" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E44" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D45" t="n">
         <v>60.13</v>
       </c>
       <c r="E45" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D46" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E46" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D47" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E47" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E48" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D49" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E49" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E50" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D51" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E51" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D52" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E52" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D53" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D54" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E54" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,40 +1580,40 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D55" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E55" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D56" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E56" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E57" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="D2" t="n">
-        <v>71.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>63.24</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>52.2</v>
+        <v>49.2</v>
       </c>
       <c r="D3" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E3" t="n">
-        <v>63.92</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>49.2</v>
+        <v>46.4</v>
       </c>
       <c r="D4" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>64.04000000000001</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D5" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E5" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D6" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D7" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E7" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D8" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E8" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D9" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D10" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D11" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E11" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D12" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E12" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D13" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E13" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,40 +719,40 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E14" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E15" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E16" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E17" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D18" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E18" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E19" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E20" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E21" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E23" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D24" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E24" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E25" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E26" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D27" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E27" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E28" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D29" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,40 +1055,40 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E30" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E31" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D32" t="n">
         <v>50.4</v>
       </c>
-      <c r="D32" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E32" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D33" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E33" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E34" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D35" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E35" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D36" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E36" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D37" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E37" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E38" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D39" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E39" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D40" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E40" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D41" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E41" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D42" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E42" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D43" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E43" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D44" t="n">
         <v>60.13</v>
       </c>
       <c r="E44" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D45" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E45" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D46" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E46" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E47" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D48" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E48" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E49" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D50" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E50" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D51" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E51" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D52" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D53" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E53" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,40 +1559,40 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D54" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E54" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D55" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E55" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E56" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D57" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,6 +1631,27 @@
         <v>67.28</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IC2607</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D58" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>74.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52.2</v>
+        <v>46.4</v>
       </c>
       <c r="D2" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>63.92</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.2</v>
+        <v>55.2</v>
       </c>
       <c r="D3" t="n">
-        <v>75.3</v>
+        <v>78.8</v>
       </c>
       <c r="E3" t="n">
-        <v>64.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="D4" t="n">
-        <v>72.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>61.4</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55.2</v>
+        <v>49.4</v>
       </c>
       <c r="D5" t="n">
-        <v>78.8</v>
+        <v>73.7</v>
       </c>
       <c r="E5" t="n">
-        <v>65.59999999999999</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57.4</v>
+        <v>40.4</v>
       </c>
       <c r="D6" t="n">
-        <v>78.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E6" t="n">
-        <v>65.76000000000001</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.4</v>
+        <v>45.6</v>
       </c>
       <c r="D7" t="n">
-        <v>73.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>63.64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D8" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>56.48</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45.6</v>
+        <v>50.4</v>
       </c>
       <c r="D9" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40.2</v>
+        <v>47.4</v>
       </c>
       <c r="D10" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E10" t="n">
-        <v>59.52</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50.4</v>
+        <v>46.8</v>
       </c>
       <c r="D11" t="n">
-        <v>71.5</v>
+        <v>67.5</v>
       </c>
       <c r="E11" t="n">
-        <v>61.32</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,61 +677,61 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>47.4</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>70.5</v>
+        <v>56.5</v>
       </c>
       <c r="E12" t="n">
-        <v>60.68</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>46.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="E13" t="n">
-        <v>58.08</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>56.5</v>
+        <v>60.6</v>
       </c>
       <c r="E14" t="n">
-        <v>52.96</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>90.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>61.1</v>
+        <v>59.45</v>
       </c>
       <c r="E15" t="n">
-        <v>54.06</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>91.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D16" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E16" t="n">
-        <v>54.77</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
       <c r="E17" t="n">
-        <v>54.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>88.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>59.3</v>
+        <v>56.65</v>
       </c>
       <c r="E18" t="n">
-        <v>53.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>84.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D19" t="n">
-        <v>57.85</v>
+        <v>55.9</v>
       </c>
       <c r="E19" t="n">
-        <v>53.74</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E21" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E22" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E23" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E24" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D25" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E25" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E26" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D27" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E27" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,61 +1013,61 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D29" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E29" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D30" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E30" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D31" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E31" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E32" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D33" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E33" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D34" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E34" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D35" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E35" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E36" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D37" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E37" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D38" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E38" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D39" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E39" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D40" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E40" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D41" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E41" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D42" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E42" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D43" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E43" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D44" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E44" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D46" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E46" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E47" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D48" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E48" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D49" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E49" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D50" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D51" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E51" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,61 +1517,61 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D52" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E52" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D53" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E53" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E54" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D55" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E56" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,34 +1622,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D57" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E57" t="n">
-        <v>67.28</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="D58" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46.4</v>
+        <v>55.2</v>
       </c>
       <c r="D2" t="n">
-        <v>72.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E2" t="n">
-        <v>61.4</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D3" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D4" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E4" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D5" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E5" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D6" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D7" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D8" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E8" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D9" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E9" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D10" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E10" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,40 +656,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E11" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E12" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E13" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E14" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D15" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E15" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E16" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E17" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D18" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E18" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E19" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E20" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D21" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E21" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D22" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E22" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E23" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D24" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E24" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E25" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D26" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,40 +992,40 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E27" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E28" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D29" t="n">
         <v>50.4</v>
       </c>
-      <c r="D29" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E29" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D30" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E30" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E31" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D32" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E32" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D33" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E33" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D34" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E34" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E35" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D36" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E36" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D37" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E37" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D38" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E38" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D39" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E39" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D40" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E40" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D41" t="n">
         <v>60.13</v>
       </c>
       <c r="E41" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D42" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E42" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D43" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E43" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E44" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D45" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E45" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E46" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D47" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E47" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D48" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E48" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D49" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D50" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E50" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,40 +1496,40 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D51" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D52" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E52" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E53" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D54" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E55" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D56" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E56" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E57" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.2</v>
+        <v>57.4</v>
       </c>
       <c r="D2" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D3" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E3" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D4" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E4" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D5" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D6" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D7" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E7" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D8" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E8" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D9" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E9" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,40 +635,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E10" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E11" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E12" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E13" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D14" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E14" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E15" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E16" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D17" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E17" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E18" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E19" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D20" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E20" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D21" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E21" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E22" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D23" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E23" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E24" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D25" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,40 +971,40 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E26" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D27" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E27" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D28" t="n">
         <v>50.4</v>
       </c>
-      <c r="D28" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E28" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D29" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E29" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E30" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D31" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E31" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D32" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E32" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D33" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E33" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E34" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D35" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E35" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E36" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D37" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E37" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D38" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E38" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D39" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E39" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D40" t="n">
         <v>60.13</v>
       </c>
       <c r="E40" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D41" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E41" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D42" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E42" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E43" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D44" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E44" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E45" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D46" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E46" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D47" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E47" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D48" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D49" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E49" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,40 +1475,40 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D50" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E50" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D51" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E51" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E52" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D53" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E54" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D55" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E55" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E56" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D57" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E57" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.4</v>
+        <v>49.4</v>
       </c>
       <c r="D2" t="n">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E2" t="n">
-        <v>65.76000000000001</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D3" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E3" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D4" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D5" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D6" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E6" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D7" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E7" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D8" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E8" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,40 +614,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E9" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E10" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E11" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E12" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D13" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E13" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E14" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E15" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D16" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E16" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E17" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E18" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D19" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E19" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E20" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E21" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D22" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E22" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E23" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D24" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,40 +950,40 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E25" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D26" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E26" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D27" t="n">
         <v>50.4</v>
       </c>
-      <c r="D27" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E27" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D28" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E28" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E29" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D30" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E30" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D31" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E31" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D32" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E32" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E33" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D34" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E34" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E35" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D36" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E36" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D37" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E37" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D38" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E38" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D39" t="n">
         <v>60.13</v>
       </c>
       <c r="E39" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D40" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E40" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D41" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E41" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E42" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D43" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E43" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E44" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D45" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E45" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D46" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E46" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D47" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D48" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E48" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,40 +1454,40 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D49" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E49" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D50" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E50" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E51" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D52" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E53" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D54" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E54" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E55" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D56" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E56" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D57" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E57" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,6 +1631,27 @@
         <v>71.40000000000001</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IC2607</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="E58" t="n">
+        <v>70.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="D2" t="n">
-        <v>73.7</v>
+        <v>61.1</v>
       </c>
       <c r="E2" t="n">
-        <v>63.64</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D3" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D4" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D5" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E5" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D6" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E6" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D7" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E7" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,40 +593,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E8" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E9" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E10" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E11" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D12" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E12" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E13" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E14" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D15" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E15" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E16" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E17" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D18" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E18" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D19" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E19" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E20" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D21" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E21" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E22" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D23" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,40 +929,40 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E25" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D26" t="n">
         <v>50.4</v>
       </c>
-      <c r="D26" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E26" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D27" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E27" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E28" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D29" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E29" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D30" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E30" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D31" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E31" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E32" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D33" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E33" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E34" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D35" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E35" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D36" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E36" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D37" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E37" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D38" t="n">
         <v>60.13</v>
       </c>
       <c r="E38" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D39" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E39" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D40" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E40" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E41" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D42" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E42" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E43" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D44" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E44" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D45" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E45" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D46" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D47" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E47" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,40 +1433,40 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D48" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E48" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D49" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E49" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E50" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D51" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E52" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D53" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E53" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E54" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D55" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E55" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D56" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E56" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D57" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D58" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.4</v>
+        <v>45.6</v>
       </c>
       <c r="D2" t="n">
-        <v>61.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>56.48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D3" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D4" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E4" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D5" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E5" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D6" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E6" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,40 +572,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E7" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E8" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E9" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E10" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D11" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E11" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E12" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E13" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E14" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E16" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E17" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E18" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D19" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E19" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E20" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D21" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E21" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,61 +887,61 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D23" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E23" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D24" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E24" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D25" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E25" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E26" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D27" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E27" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D28" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E28" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D29" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E29" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E30" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D31" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E31" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D32" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E32" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D33" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E33" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D34" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E34" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D35" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E35" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D36" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E36" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D37" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E37" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D38" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E38" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E39" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D40" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E40" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E41" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D42" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E42" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D43" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E43" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D44" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D45" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E45" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,61 +1391,61 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D46" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E46" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D47" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E47" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E48" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D49" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E50" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D51" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E51" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E52" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D53" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E53" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D54" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E54" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D55" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D56" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,34 +1622,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D57" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E57" t="n">
-        <v>70.84</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="D58" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="E58" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45.6</v>
+        <v>40.2</v>
       </c>
       <c r="D2" t="n">
-        <v>71.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D3" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E3" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D4" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E4" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D5" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E5" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,40 +551,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E6" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E7" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E8" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E9" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D10" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E10" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E11" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E12" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E13" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E15" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D16" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E16" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="17">
@@ -1629,6 +1629,27 @@
       </c>
       <c r="E57" t="n">
         <v>71.44</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IC2607</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>71</v>
+      </c>
+      <c r="D58" t="n">
+        <v>63</v>
+      </c>
+      <c r="E58" t="n">
+        <v>64.36</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.2</v>
+        <v>50.4</v>
       </c>
       <c r="D2" t="n">
-        <v>65.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E2" t="n">
-        <v>59.52</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.4</v>
+        <v>47.4</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="E3" t="n">
-        <v>61.32</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="D4" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="E4" t="n">
-        <v>60.68</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,40 +530,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E5" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E6" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E7" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E8" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D9" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E9" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E10" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E11" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E12" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E14" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D15" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E15" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E16" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E17" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D18" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E18" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E19" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D20" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,40 +866,40 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E21" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E22" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D23" t="n">
         <v>50.4</v>
       </c>
-      <c r="D23" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E23" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D24" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E24" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E25" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D26" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E26" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D27" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E27" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D28" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E28" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E29" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D30" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E30" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E31" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D32" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E32" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D33" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E33" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D34" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E34" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D35" t="n">
         <v>60.13</v>
       </c>
       <c r="E35" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D36" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E36" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D37" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E37" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E38" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D39" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E39" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E40" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D41" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E41" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D42" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E42" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D43" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D44" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E44" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,40 +1370,40 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D45" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E45" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D46" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E46" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E47" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D48" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E49" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D50" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E50" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E51" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D52" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E52" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D53" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E53" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D54" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D55" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D56" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E56" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D57" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E57" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E58" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,27 @@
         <v>60.52</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IC2607</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="E59" t="n">
+        <v>65.04000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50.4</v>
+        <v>46.8</v>
       </c>
       <c r="D2" t="n">
-        <v>71.5</v>
+        <v>67.5</v>
       </c>
       <c r="E2" t="n">
-        <v>61.32</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47.4</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>70.5</v>
+        <v>56.5</v>
       </c>
       <c r="E3" t="n">
-        <v>60.68</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>67.5</v>
+        <v>61.1</v>
       </c>
       <c r="E4" t="n">
-        <v>58.08</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>56.5</v>
+        <v>60.6</v>
       </c>
       <c r="E5" t="n">
-        <v>52.96</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>61.1</v>
+        <v>59.45</v>
       </c>
       <c r="E6" t="n">
-        <v>54.06</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>91.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D7" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E7" t="n">
-        <v>54.77</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
       <c r="E8" t="n">
-        <v>54.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>88.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>59.3</v>
+        <v>56.65</v>
       </c>
       <c r="E9" t="n">
-        <v>53.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D10" t="n">
-        <v>57.85</v>
+        <v>55.9</v>
       </c>
       <c r="E10" t="n">
-        <v>53.74</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E12" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E13" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E14" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E15" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D16" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E16" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E17" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D18" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E18" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,61 +824,61 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D20" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E20" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E21" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D22" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E22" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E23" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D24" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E24" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D25" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E25" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D26" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E26" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E27" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D28" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E28" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D29" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E29" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D30" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E30" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D31" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E31" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D32" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E32" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D33" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E33" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D34" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E34" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D35" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E35" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D37" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E37" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E38" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D39" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E39" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D40" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E40" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D41" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D42" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E42" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,61 +1328,61 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D43" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E43" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D44" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E44" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E45" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D46" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E47" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D48" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E48" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E49" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D50" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E50" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D51" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E51" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D52" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D53" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D54" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E54" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D55" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E55" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E56" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D57" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,34 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D58" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E58" t="n">
-        <v>60.52</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="D59" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="E59" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,40 +467,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46.8</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>67.5</v>
+        <v>56.5</v>
       </c>
       <c r="E2" t="n">
-        <v>58.08</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E3" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E4" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E5" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D6" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E6" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E7" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E8" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D9" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E9" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E10" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E11" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D12" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E12" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E13" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E14" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D15" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E15" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E16" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D17" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,40 +803,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E19" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D20" t="n">
         <v>50.4</v>
       </c>
-      <c r="D20" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E20" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D21" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E21" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E22" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D23" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E23" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D24" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E24" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D25" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E25" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E26" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D27" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E27" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D28" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E28" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D29" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E29" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D30" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E30" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D31" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E31" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D32" t="n">
         <v>60.13</v>
       </c>
       <c r="E32" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D33" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E33" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D34" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E34" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E35" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E36" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E37" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D38" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E38" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D39" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E39" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D40" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D41" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E41" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,40 +1307,40 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D42" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E42" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D43" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E43" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E44" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D45" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E46" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D47" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E47" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E48" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D49" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E49" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D50" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E50" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D51" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D52" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D53" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E53" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D54" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E54" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E55" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D56" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D56" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E56" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D57" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E57" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D58" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,28 +458,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IC2604</t>
+          <t>IC2605</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>56.5</v>
+        <v>61.1</v>
       </c>
       <c r="E2" t="n">
-        <v>52.96</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E3" t="n">
-        <v>54.06</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>91.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>60.6</v>
+        <v>59.45</v>
       </c>
       <c r="E4" t="n">
-        <v>54.77</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D5" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E5" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E6" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E7" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D8" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E8" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E10" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D11" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E11" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E12" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E13" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D14" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E14" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E15" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D16" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,40 +782,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E17" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E18" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D19" t="n">
         <v>50.4</v>
       </c>
-      <c r="D19" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E19" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D20" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E20" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E21" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D22" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E22" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D23" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E23" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D24" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E24" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E25" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D26" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E26" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D27" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E27" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D28" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E28" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D29" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E29" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D30" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E30" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D31" t="n">
         <v>60.13</v>
       </c>
       <c r="E31" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D32" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E32" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D33" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E33" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E34" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D35" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E35" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E36" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D37" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E37" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D38" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E38" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D40" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E40" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,40 +1286,40 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D41" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E41" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D42" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E42" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E43" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D44" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E45" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D46" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E46" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E47" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D48" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E48" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D49" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E49" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D50" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D51" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D52" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E52" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D53" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E54" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D55" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D55" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E55" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D56" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E56" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D57" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E58" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,27 @@
         <v>60.16</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IC2607</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>54.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>90.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>61.1</v>
+        <v>59.45</v>
       </c>
       <c r="E2" t="n">
-        <v>54.06</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>91.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D3" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E3" t="n">
-        <v>54.77</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
       <c r="E4" t="n">
-        <v>54.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>88.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>59.3</v>
+        <v>56.65</v>
       </c>
       <c r="E5" t="n">
-        <v>53.71</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>84.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D6" t="n">
-        <v>57.85</v>
+        <v>55.9</v>
       </c>
       <c r="E6" t="n">
-        <v>53.74</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E7" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E8" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E9" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E10" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E11" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D12" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E12" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E13" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D14" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E14" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,61 +740,61 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D16" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E16" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E17" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D18" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E18" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E19" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D20" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E20" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D21" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E21" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D22" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E22" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E23" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D24" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E24" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D25" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E25" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D26" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E26" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D27" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E27" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E28" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D29" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E29" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D30" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E30" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D31" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E31" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E32" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D33" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E33" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E34" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D35" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E35" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D36" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E36" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D37" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D38" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E38" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,61 +1244,61 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D39" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E39" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D40" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E40" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E41" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D42" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E43" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D44" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E44" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E45" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D46" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E46" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E47" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D48" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D49" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D50" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E50" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D51" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E51" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E52" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D53" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D54" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E54" t="n">
-        <v>60.52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="D55" t="n">
-        <v>68.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="E55" t="n">
-        <v>65.04000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E56" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,54 +1622,12 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D57" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E57" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D58" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D59" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E59" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="n">
-        <v>59.45</v>
+        <v>59.3</v>
       </c>
       <c r="E2" t="n">
-        <v>54.71</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E3" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>84.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D4" t="n">
-        <v>57.85</v>
+        <v>55.9</v>
       </c>
       <c r="E4" t="n">
-        <v>53.74</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E6" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E7" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E8" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E9" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D10" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E10" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E11" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D12" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E12" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,61 +698,61 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D14" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E14" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E15" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D16" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E16" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E17" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D18" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E18" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D19" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E19" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D20" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E20" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E21" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D22" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E22" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D23" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E23" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D24" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E24" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D25" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E25" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D26" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E26" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D27" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E27" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D28" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E28" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D29" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E29" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E30" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D31" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E31" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E32" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D33" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E33" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D34" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E34" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D35" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D36" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E36" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,61 +1202,61 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D37" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E37" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D38" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E39" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D40" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E41" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D42" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E42" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E43" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D44" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E44" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D45" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E45" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D46" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D47" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D48" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E48" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D49" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E49" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E50" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D51" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D52" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E52" t="n">
-        <v>60.52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="D53" t="n">
-        <v>68.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="E53" t="n">
-        <v>65.04000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E54" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1580,54 +1580,12 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D55" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E55" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D56" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E56" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D57" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E57" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>59.3</v>
+        <v>57.85</v>
       </c>
       <c r="E2" t="n">
-        <v>53.71</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E3" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="4">

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>57.85</v>
+        <v>56.65</v>
       </c>
       <c r="E2" t="n">
-        <v>53.74</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D3" t="n">
-        <v>56.65</v>
+        <v>55.9</v>
       </c>
       <c r="E3" t="n">
-        <v>52.86</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E4" t="n">
-        <v>52.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E5" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D6" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E6" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E7" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E8" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D9" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E9" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E10" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D11" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,40 +677,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E12" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E13" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D14" t="n">
         <v>50.4</v>
       </c>
-      <c r="D14" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E14" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D15" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E15" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E16" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D17" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E17" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D18" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E18" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D19" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E19" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E20" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D21" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E21" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D22" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E22" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D23" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E23" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D24" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E24" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E25" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D26" t="n">
         <v>60.13</v>
       </c>
       <c r="E26" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D27" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E27" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D28" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E28" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E29" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D30" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E30" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E31" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D32" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E32" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D33" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E33" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D34" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D35" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E35" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,40 +1181,40 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D36" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E36" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D37" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E37" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E38" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D39" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E40" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D41" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E41" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E42" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D43" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E43" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D44" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E44" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D45" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D46" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D47" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E47" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D48" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E49" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,19 +1475,19 @@
         </is>
       </c>
       <c r="C50" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D50" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D50" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E50" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D51" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E51" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D52" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E53" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1559,33 +1559,12 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D54" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E54" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D55" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E55" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>56.65</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>52.86</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>55.9</v>
+        <v>52.75</v>
       </c>
       <c r="E3" t="n">
-        <v>52.06</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="E4" t="n">
-        <v>50.09</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="D5" t="n">
-        <v>52.75</v>
+        <v>48.7</v>
       </c>
       <c r="E5" t="n">
-        <v>49.06</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="E6" t="n">
-        <v>47.49</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>74.8</v>
       </c>
       <c r="D7" t="n">
-        <v>48.7</v>
+        <v>53.5</v>
       </c>
       <c r="E7" t="n">
-        <v>45.34</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>66.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>49.2</v>
+        <v>54.75</v>
       </c>
       <c r="E8" t="n">
-        <v>46.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D9" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E9" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,61 +635,61 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>79.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>54.75</v>
+        <v>55</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70.2</v>
+        <v>50.4</v>
       </c>
       <c r="D11" t="n">
-        <v>52.6</v>
+        <v>49.07</v>
       </c>
       <c r="E11" t="n">
-        <v>48.74</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>80.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>50.4</v>
       </c>
       <c r="E12" t="n">
-        <v>50.09</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D13" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E13" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E14" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D15" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E15" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D16" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E16" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D17" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E17" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E18" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D19" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E19" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D20" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E20" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D21" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E21" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E22" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D23" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E23" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D24" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E24" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D25" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E25" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D26" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E26" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E27" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D28" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E28" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E29" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E30" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D31" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E31" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D32" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D33" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E33" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,61 +1139,61 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D34" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E34" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D35" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E35" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E36" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D37" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E38" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D39" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E39" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E40" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D41" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E41" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D42" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E42" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D43" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D44" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D45" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E45" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D46" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E46" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E47" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D48" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>68.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>59.6</v>
+        <v>57.3</v>
       </c>
       <c r="E49" t="n">
-        <v>60.52</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,96 +1475,12 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>80.2</v>
+        <v>52.2</v>
       </c>
       <c r="D50" t="n">
-        <v>68.59999999999999</v>
+        <v>47.3</v>
       </c>
       <c r="E50" t="n">
-        <v>65.04000000000001</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="D51" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="E51" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="D52" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="E52" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D53" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E53" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D54" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E54" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>74.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>52.75</v>
       </c>
       <c r="E2" t="n">
-        <v>50.09</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D3" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E3" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D4" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E4" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E5" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D6" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E6" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E7" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D8" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,40 +614,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E10" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D11" t="n">
         <v>50.4</v>
       </c>
-      <c r="D11" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E11" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D12" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E12" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E13" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D14" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E14" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D15" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E15" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D16" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E16" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E17" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D18" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E18" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D19" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E19" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D20" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E20" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E21" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D22" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E22" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D23" t="n">
         <v>60.13</v>
       </c>
       <c r="E23" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D24" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E24" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D25" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E25" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E26" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E27" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E28" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D29" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E29" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D30" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E30" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D31" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D32" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E32" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,40 +1118,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D33" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D34" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E34" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E35" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D36" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E37" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D38" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E38" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E39" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D40" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E40" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D41" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E41" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D42" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D43" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D44" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E44" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D45" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E45" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E46" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D47" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D47" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E47" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D48" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E48" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,33 +1454,54 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>64.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D49" t="n">
-        <v>57.3</v>
+        <v>62.5</v>
       </c>
       <c r="E49" t="n">
-        <v>60.16</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IC2607</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D50" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>60.16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IC2607</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
         <v>52.2</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D51" t="n">
         <v>47.3</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E51" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="D2" t="n">
-        <v>52.75</v>
+        <v>50.8</v>
       </c>
       <c r="E2" t="n">
-        <v>49.06</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D3" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E3" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E4" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D5" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E5" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E6" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D7" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,40 +593,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E9" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D10" t="n">
         <v>50.4</v>
       </c>
-      <c r="D10" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E10" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D11" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E11" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E12" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D13" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E13" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D14" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E14" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D15" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E15" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E16" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D17" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E17" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D18" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E18" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D19" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E19" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D20" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E20" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D21" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E21" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D22" t="n">
         <v>60.13</v>
       </c>
       <c r="E22" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D23" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E23" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D24" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E24" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E25" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E26" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E27" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D28" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E28" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D29" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E29" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D30" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D31" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E31" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,40 +1097,40 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D32" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E32" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D33" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E33" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E34" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D35" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E36" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D37" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E37" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E38" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D39" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E39" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D40" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E40" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D41" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D42" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D43" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E43" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D44" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E44" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E45" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D46" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D46" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E46" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D47" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E47" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D48" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E48" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E49" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,33 +1475,12 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D50" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E50" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D51" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E51" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72.8</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="E2" t="n">
-        <v>47.49</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E3" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D4" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E4" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E5" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D6" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,40 +572,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E8" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D9" t="n">
         <v>50.4</v>
       </c>
-      <c r="D9" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E9" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D10" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E10" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E11" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D12" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E12" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D13" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E13" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D14" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E14" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E15" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D16" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E16" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E17" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D18" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E18" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E19" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D20" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E20" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D21" t="n">
         <v>60.13</v>
       </c>
       <c r="E21" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D22" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E22" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D24" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E24" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E25" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D26" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E26" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D27" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E27" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D28" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D29" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E29" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,61 +1055,61 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D30" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E30" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D31" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E31" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E32" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D33" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E34" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D35" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E35" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E36" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D37" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E37" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D38" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E38" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D39" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D40" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D41" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E41" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D42" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E42" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E43" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D44" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D45" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E45" t="n">
-        <v>60.52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="D46" t="n">
-        <v>68.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="E46" t="n">
-        <v>65.04000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E47" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1433,54 +1433,12 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D48" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E48" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D49" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E49" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D50" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E50" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="E2" t="n">
-        <v>45.34</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D3" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E3" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E4" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D5" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,40 +551,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E7" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D8" t="n">
         <v>50.4</v>
       </c>
-      <c r="D8" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E8" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D9" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E9" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E10" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D11" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E11" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D12" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E12" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D13" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E13" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E14" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D15" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E15" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E16" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D17" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E17" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E18" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E19" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D20" t="n">
         <v>60.13</v>
       </c>
       <c r="E20" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,13 +866,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D21" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E21" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="22">

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D2" t="n">
-        <v>49.2</v>
+        <v>53.5</v>
       </c>
       <c r="E2" t="n">
-        <v>46.11</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>53.5</v>
+        <v>54.75</v>
       </c>
       <c r="E3" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>79.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D4" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,40 +530,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E6" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D7" t="n">
         <v>50.4</v>
       </c>
-      <c r="D7" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E7" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D8" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E8" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E9" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D10" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E10" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D11" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E11" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D12" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E12" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E13" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D14" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E14" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E15" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D16" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E16" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E17" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E18" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D19" t="n">
         <v>60.13</v>
       </c>
       <c r="E19" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D20" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E20" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D21" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E21" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E23" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E24" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D25" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E25" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D26" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E26" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D27" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D28" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E28" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,40 +1034,40 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D29" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E29" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D30" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E30" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E31" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D32" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E33" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D34" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E34" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E35" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D36" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E36" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D37" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E37" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D38" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D39" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D40" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E40" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D41" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E41" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E42" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D43" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D43" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E43" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D44" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E44" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D45" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E45" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E46" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,33 +1412,12 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D47" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E47" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D48" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E48" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,82 +467,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="D2" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E2" t="n">
-        <v>49.69</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D3" t="n">
-        <v>54.75</v>
+        <v>49.07</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70.2</v>
+        <v>50.6</v>
       </c>
       <c r="D4" t="n">
-        <v>52.6</v>
+        <v>50.4</v>
       </c>
       <c r="E4" t="n">
-        <v>48.74</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>80.59999999999999</v>
+        <v>59.4</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>57.13</v>
       </c>
       <c r="E5" t="n">
-        <v>50.09</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>49.07</v>
+        <v>53.33</v>
       </c>
       <c r="E6" t="n">
-        <v>47.8</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.6</v>
+        <v>57.2</v>
       </c>
       <c r="D7" t="n">
-        <v>50.4</v>
+        <v>54.6</v>
       </c>
       <c r="E7" t="n">
-        <v>49.17</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>59.4</v>
+        <v>57.4</v>
       </c>
       <c r="D8" t="n">
-        <v>57.13</v>
+        <v>59.27</v>
       </c>
       <c r="E8" t="n">
-        <v>52.37</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>66.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="D9" t="n">
-        <v>53.33</v>
+        <v>60.8</v>
       </c>
       <c r="E9" t="n">
-        <v>51.8</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>57.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>54.6</v>
+        <v>59.73</v>
       </c>
       <c r="E10" t="n">
-        <v>52.93</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>57.4</v>
+        <v>56.4</v>
       </c>
       <c r="D11" t="n">
-        <v>59.27</v>
+        <v>61.4</v>
       </c>
       <c r="E11" t="n">
-        <v>55.2</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>60.8</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
-        <v>60.8</v>
+        <v>63.53</v>
       </c>
       <c r="E12" t="n">
-        <v>56.87</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>64.40000000000001</v>
+        <v>55.4</v>
       </c>
       <c r="D13" t="n">
-        <v>59.73</v>
+        <v>60.4</v>
       </c>
       <c r="E13" t="n">
-        <v>56.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>56.4</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>61.4</v>
+        <v>57.87</v>
       </c>
       <c r="E14" t="n">
-        <v>58.53</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>63.53</v>
+        <v>60.13</v>
       </c>
       <c r="E15" t="n">
-        <v>60.47</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>55.4</v>
+        <v>56.4</v>
       </c>
       <c r="D16" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E16" t="n">
-        <v>56.87</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>57</v>
+        <v>63.4</v>
       </c>
       <c r="D17" t="n">
-        <v>57.87</v>
+        <v>63.27</v>
       </c>
       <c r="E17" t="n">
-        <v>56.07</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>58.4</v>
       </c>
       <c r="D18" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E18" t="n">
-        <v>57.2</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>56.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>60.13</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
-        <v>58.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63.4</v>
+        <v>64.2</v>
       </c>
       <c r="D20" t="n">
-        <v>63.27</v>
+        <v>64.2</v>
       </c>
       <c r="E20" t="n">
-        <v>60.3</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>58.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>59.87</v>
+        <v>63.27</v>
       </c>
       <c r="E21" t="n">
-        <v>57.03</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>67.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>63.2</v>
       </c>
       <c r="E22" t="n">
-        <v>61.67</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>64.2</v>
+        <v>66.2</v>
       </c>
       <c r="D23" t="n">
-        <v>64.2</v>
+        <v>59.4</v>
       </c>
       <c r="E23" t="n">
-        <v>62.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>65.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="D24" t="n">
-        <v>63.27</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>61.77</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>66</v>
+        <v>67.8</v>
       </c>
       <c r="D25" t="n">
-        <v>63.2</v>
+        <v>61.4</v>
       </c>
       <c r="E25" t="n">
-        <v>61.37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,82 +971,82 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>66.2</v>
+        <v>62.8</v>
       </c>
       <c r="D26" t="n">
-        <v>59.4</v>
+        <v>55.13</v>
       </c>
       <c r="E26" t="n">
-        <v>59.47</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>75</v>
+        <v>61.8</v>
       </c>
       <c r="D27" t="n">
-        <v>65.93000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="E27" t="n">
-        <v>62.97</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>67.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>61.4</v>
+        <v>66.3</v>
       </c>
       <c r="E28" t="n">
-        <v>61</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>62.8</v>
+        <v>67.8</v>
       </c>
       <c r="D29" t="n">
-        <v>55.13</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>56.9</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>61.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>68.5</v>
+        <v>84.3</v>
       </c>
       <c r="E30" t="n">
-        <v>64.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>68.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D31" t="n">
-        <v>66.3</v>
+        <v>88.8</v>
       </c>
       <c r="E31" t="n">
-        <v>64.95999999999999</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>67.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>71.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="E32" t="n">
-        <v>67.28</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>89.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D33" t="n">
-        <v>84.3</v>
+        <v>87</v>
       </c>
       <c r="E33" t="n">
-        <v>74.16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>93.8</v>
+        <v>82</v>
       </c>
       <c r="D34" t="n">
-        <v>88.8</v>
+        <v>75.5</v>
       </c>
       <c r="E34" t="n">
-        <v>78.04000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>83.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="D35" t="n">
-        <v>82.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>76.76000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>92</v>
+        <v>86.8</v>
       </c>
       <c r="D36" t="n">
-        <v>87</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>79</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D37" t="n">
-        <v>75.5</v>
+        <v>75.3</v>
       </c>
       <c r="E37" t="n">
-        <v>71.40000000000001</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>80.8</v>
+        <v>71</v>
       </c>
       <c r="D38" t="n">
-        <v>75.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="E38" t="n">
-        <v>70.84</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>86.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>78.90000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="E39" t="n">
-        <v>72.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>85</v>
+        <v>80.2</v>
       </c>
       <c r="D40" t="n">
-        <v>75.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>71.44</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>71</v>
+        <v>62.8</v>
       </c>
       <c r="D41" t="n">
-        <v>63</v>
+        <v>58.6</v>
       </c>
       <c r="E41" t="n">
-        <v>64.36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>68.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="D42" t="n">
-        <v>59.6</v>
+        <v>62.5</v>
       </c>
       <c r="E42" t="n">
-        <v>60.52</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,97 +1328,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>80.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>68.59999999999999</v>
+        <v>57.3</v>
       </c>
       <c r="E43" t="n">
-        <v>65.04000000000001</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="D44" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="E44" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="D45" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="E45" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D46" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E46" t="n">
         <v>60.16</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D47" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E47" t="n">
-        <v>54.08</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>70.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>48.74</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="3">
@@ -1335,6 +1335,27 @@
       </c>
       <c r="E43" t="n">
         <v>60.16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>IC2607</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>54.08</v>
       </c>
     </row>
   </sheetData>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,28 +458,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IC2605</t>
+          <t>IC2606</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>49.07</v>
       </c>
       <c r="E2" t="n">
-        <v>50.09</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D3" t="n">
         <v>50.4</v>
       </c>
-      <c r="D3" t="n">
-        <v>49.07</v>
-      </c>
       <c r="E3" t="n">
-        <v>47.8</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.6</v>
+        <v>59.4</v>
       </c>
       <c r="D4" t="n">
-        <v>50.4</v>
+        <v>57.13</v>
       </c>
       <c r="E4" t="n">
-        <v>49.17</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E5" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D6" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E6" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D7" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E7" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D8" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E8" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E9" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D10" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E10" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E11" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D12" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E12" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E13" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E14" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D15" t="n">
         <v>60.13</v>
       </c>
       <c r="E15" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D16" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E16" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D17" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E17" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E19" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E20" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D21" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E21" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D22" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E22" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D23" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D24" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E24" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,40 +950,40 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D25" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D26" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E26" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E27" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D28" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E29" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D30" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E30" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E31" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D32" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E32" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D33" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E33" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D34" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D35" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E36" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D37" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E37" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E38" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D39" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D39" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E39" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D40" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E40" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D41" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E41" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E42" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1328,33 +1328,12 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D43" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E43" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E44" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50.4</v>
+        <v>59.4</v>
       </c>
       <c r="D2" t="n">
-        <v>49.07</v>
+        <v>57.13</v>
       </c>
       <c r="E2" t="n">
-        <v>47.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>50.4</v>
+        <v>53.33</v>
       </c>
       <c r="E3" t="n">
-        <v>49.17</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>59.4</v>
+        <v>57.2</v>
       </c>
       <c r="D4" t="n">
-        <v>57.13</v>
+        <v>54.6</v>
       </c>
       <c r="E4" t="n">
-        <v>52.37</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>66.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D5" t="n">
-        <v>53.33</v>
+        <v>59.27</v>
       </c>
       <c r="E5" t="n">
-        <v>51.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="D6" t="n">
-        <v>54.6</v>
+        <v>60.8</v>
       </c>
       <c r="E6" t="n">
-        <v>52.93</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E7" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D8" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E8" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D9" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E9" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D10" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E10" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E11" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E12" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D13" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E13" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D14" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E14" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D15" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E15" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E16" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D17" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E17" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E18" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D19" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E19" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D20" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E20" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D22" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E22" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,61 +908,61 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D23" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E23" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D24" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E24" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E25" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D26" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E27" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D28" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E28" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E29" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D30" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E30" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D31" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E31" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D32" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D33" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D34" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E34" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D35" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E35" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E36" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D37" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D38" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E38" t="n">
-        <v>60.52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="D39" t="n">
-        <v>68.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="E39" t="n">
-        <v>65.04000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1286,54 +1286,12 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D41" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E41" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D42" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E42" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D43" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E43" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>59.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>57.13</v>
+        <v>53.33</v>
       </c>
       <c r="E2" t="n">
-        <v>52.37</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D3" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E3" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D4" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E4" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D5" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E5" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E6" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D7" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E7" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E8" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D9" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E9" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D10" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E10" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D11" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E11" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D12" t="n">
         <v>60.13</v>
       </c>
       <c r="E12" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D13" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E13" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D14" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E14" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E15" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E16" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E17" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E18" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D19" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E19" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D20" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D21" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E21" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D22" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E22" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D23" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E23" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E24" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D25" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E26" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D27" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E27" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E28" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D29" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E29" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D30" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E30" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D31" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D32" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E33" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D34" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E34" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E35" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D36" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D36" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E36" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D37" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E37" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D38" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E39" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1265,33 +1265,12 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D40" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E40" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D41" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E41" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="D2" t="n">
-        <v>53.33</v>
+        <v>54.6</v>
       </c>
       <c r="E2" t="n">
-        <v>51.8</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D3" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E3" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D4" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E4" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E5" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D6" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E6" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E7" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D8" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E8" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E9" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D10" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E10" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D11" t="n">
         <v>60.13</v>
       </c>
       <c r="E11" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D12" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E12" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D13" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E13" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E15" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E16" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D17" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E17" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D18" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E18" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D20" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E20" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,40 +866,40 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D21" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E21" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D22" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E22" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E23" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D24" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E25" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D26" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E26" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E27" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D28" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E28" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D29" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E29" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D30" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D31" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D32" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E32" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D33" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E33" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E34" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D35" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D35" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E35" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D36" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E36" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D37" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E38" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1244,33 +1244,12 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D39" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E39" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D40" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E40" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="D2" t="n">
-        <v>54.6</v>
+        <v>59.27</v>
       </c>
       <c r="E2" t="n">
-        <v>52.93</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="D3" t="n">
-        <v>59.27</v>
+        <v>60.8</v>
       </c>
       <c r="E3" t="n">
-        <v>55.2</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>60.8</v>
+        <v>59.73</v>
       </c>
       <c r="E4" t="n">
-        <v>56.87</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D5" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E5" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E6" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D7" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E7" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D8" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E8" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D9" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E9" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D10" t="n">
         <v>60.13</v>
       </c>
       <c r="E10" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D11" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E11" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D12" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E12" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E14" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E15" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E16" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D17" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E17" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D19" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E19" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,40 +845,40 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D20" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D21" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E21" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E22" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D23" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E24" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D25" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E25" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E26" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D27" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E27" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D28" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E28" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D29" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D30" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E31" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D32" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E32" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E33" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D34" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D34" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E34" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D35" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E35" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D36" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E37" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1223,33 +1223,12 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D38" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E38" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E39" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>59.27</v>
+        <v>59.73</v>
       </c>
       <c r="E2" t="n">
-        <v>55.2</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60.8</v>
+        <v>56.4</v>
       </c>
       <c r="D3" t="n">
-        <v>60.8</v>
+        <v>61.4</v>
       </c>
       <c r="E3" t="n">
-        <v>56.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
-        <v>59.73</v>
+        <v>63.53</v>
       </c>
       <c r="E4" t="n">
-        <v>56.47</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56.4</v>
+        <v>55.4</v>
       </c>
       <c r="D5" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="E5" t="n">
-        <v>58.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D6" t="n">
-        <v>63.53</v>
+        <v>57.87</v>
       </c>
       <c r="E6" t="n">
-        <v>60.47</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D7" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E7" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D8" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E8" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D9" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E9" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D10" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E10" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D12" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E12" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E13" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E14" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D15" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E15" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D16" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D17" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E17" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,61 +803,61 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D18" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E18" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D19" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E19" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E20" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D21" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E22" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D23" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E23" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E24" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D25" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E25" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D26" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E26" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D27" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D28" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D29" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E29" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D30" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E30" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E31" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D32" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D33" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E33" t="n">
-        <v>60.52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="D34" t="n">
-        <v>68.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="E34" t="n">
-        <v>65.04000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1181,54 +1181,12 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D36" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E36" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D37" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E37" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E38" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="D2" t="n">
-        <v>59.73</v>
+        <v>61.4</v>
       </c>
       <c r="E2" t="n">
-        <v>56.47</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E3" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D4" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E4" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E5" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D6" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E6" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D7" t="n">
         <v>60.13</v>
       </c>
       <c r="E7" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D8" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E8" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D9" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E9" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E10" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D11" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E11" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E12" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E13" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D14" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E14" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D16" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E16" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,40 +782,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D17" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E17" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D18" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E18" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E19" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D20" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E21" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D22" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E22" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E23" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D24" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E24" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D25" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E25" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D26" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D27" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D28" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E28" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D29" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E29" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E30" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D31" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D31" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E31" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D32" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E32" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D33" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E33" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E34" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1160,33 +1160,12 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D35" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E35" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D36" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E36" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56.4</v>
+        <v>67</v>
       </c>
       <c r="D2" t="n">
-        <v>61.4</v>
+        <v>63.53</v>
       </c>
       <c r="E2" t="n">
-        <v>58.53</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D3" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E3" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D4" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E4" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D5" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E5" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D6" t="n">
         <v>60.13</v>
       </c>
       <c r="E6" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D7" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E7" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D8" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E8" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D10" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E10" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E11" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E12" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D13" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E13" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D15" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E15" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,40 +761,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D16" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E16" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D17" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E17" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E18" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D19" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E20" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D21" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E21" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E22" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D23" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E23" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D24" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E24" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D25" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D26" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D27" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E27" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D28" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E28" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E29" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D30" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D30" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E30" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D31" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E31" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D32" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E32" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E33" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1139,33 +1139,12 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D34" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E34" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E35" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>55.4</v>
       </c>
       <c r="D2" t="n">
-        <v>63.53</v>
+        <v>60.4</v>
       </c>
       <c r="E2" t="n">
-        <v>60.47</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.4</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>60.4</v>
+        <v>57.87</v>
       </c>
       <c r="E3" t="n">
-        <v>56.87</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E4" t="n">
-        <v>56.07</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D5" t="n">
         <v>60.13</v>
       </c>
       <c r="E5" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D6" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E6" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D7" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E7" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E9" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E10" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D11" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E11" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D12" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E12" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D14" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E14" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,40 +740,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D15" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E15" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D16" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E16" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E17" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D18" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E19" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D20" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E20" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E21" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D22" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E22" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D23" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D24" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D25" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D26" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E26" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D27" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E27" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E28" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D29" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D29" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E29" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D30" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E30" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D31" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E32" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1118,33 +1118,12 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D33" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E33" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E34" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.4</v>
+        <v>63</v>
       </c>
       <c r="D2" t="n">
-        <v>60.4</v>
+        <v>60.13</v>
       </c>
       <c r="E2" t="n">
-        <v>56.87</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="D3" t="n">
-        <v>57.87</v>
+        <v>60.13</v>
       </c>
       <c r="E3" t="n">
-        <v>56.07</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="D4" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E4" t="n">
-        <v>57.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56.4</v>
+        <v>58.4</v>
       </c>
       <c r="D5" t="n">
-        <v>60.13</v>
+        <v>59.87</v>
       </c>
       <c r="E5" t="n">
-        <v>58.03</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>63.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
-        <v>60.3</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58.4</v>
+        <v>64.2</v>
       </c>
       <c r="D7" t="n">
-        <v>59.87</v>
+        <v>64.2</v>
       </c>
       <c r="E7" t="n">
-        <v>57.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>64</v>
+        <v>63.27</v>
       </c>
       <c r="E8" t="n">
-        <v>61.67</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="D9" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="E9" t="n">
-        <v>62.37</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="D10" t="n">
-        <v>63.27</v>
+        <v>59.4</v>
       </c>
       <c r="E10" t="n">
-        <v>61.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>63.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>61.37</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
       <c r="D12" t="n">
-        <v>59.4</v>
+        <v>61.4</v>
       </c>
       <c r="E12" t="n">
-        <v>59.47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,61 +698,61 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="D13" t="n">
-        <v>65.93000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="E13" t="n">
-        <v>62.97</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67.8</v>
+        <v>61.8</v>
       </c>
       <c r="D14" t="n">
-        <v>61.4</v>
+        <v>68.5</v>
       </c>
       <c r="E14" t="n">
-        <v>61</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>62.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>55.13</v>
+        <v>66.3</v>
       </c>
       <c r="E15" t="n">
-        <v>56.9</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>61.8</v>
+        <v>67.8</v>
       </c>
       <c r="D16" t="n">
-        <v>68.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>64.28</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>68.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>66.3</v>
+        <v>84.3</v>
       </c>
       <c r="E17" t="n">
-        <v>64.95999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>67.8</v>
+        <v>93.8</v>
       </c>
       <c r="D18" t="n">
-        <v>71.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E18" t="n">
-        <v>67.28</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>84.3</v>
+        <v>82.2</v>
       </c>
       <c r="E19" t="n">
-        <v>74.16</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="D20" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="E20" t="n">
-        <v>78.04000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D21" t="n">
-        <v>82.2</v>
+        <v>75.5</v>
       </c>
       <c r="E21" t="n">
-        <v>76.76000000000001</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>92</v>
+        <v>80.8</v>
       </c>
       <c r="D22" t="n">
-        <v>87</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>82</v>
+        <v>86.8</v>
       </c>
       <c r="D23" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>71.40000000000001</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80.8</v>
+        <v>85</v>
       </c>
       <c r="D24" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E24" t="n">
-        <v>70.84</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>86.8</v>
+        <v>71</v>
       </c>
       <c r="D25" t="n">
-        <v>78.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="E25" t="n">
-        <v>72.36</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>85</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E26" t="n">
-        <v>71.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>71</v>
+        <v>80.2</v>
       </c>
       <c r="D27" t="n">
-        <v>63</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>64.36</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="D28" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="E28" t="n">
-        <v>60.52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="D29" t="n">
-        <v>68.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="E29" t="n">
-        <v>65.04000000000001</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>58.6</v>
+        <v>57.3</v>
       </c>
       <c r="E30" t="n">
-        <v>60</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1076,54 +1076,12 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="D31" t="n">
-        <v>62.5</v>
+        <v>47.3</v>
       </c>
       <c r="E31" t="n">
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D32" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E32" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D33" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E33" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>63</v>
+        <v>56.4</v>
       </c>
       <c r="D2" t="n">
         <v>60.13</v>
       </c>
       <c r="E2" t="n">
-        <v>57.2</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D3" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E3" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D4" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E4" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E6" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E7" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E8" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D9" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E9" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D11" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E11" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,40 +677,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D12" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D13" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E13" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E14" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D15" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E16" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D17" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E17" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E18" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D19" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E19" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D20" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D21" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D22" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D23" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E23" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D24" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E24" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E25" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D26" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D26" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E26" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D27" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E27" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D28" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,19 +1034,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E29" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1055,33 +1055,12 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D30" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E30" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D31" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E31" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56.4</v>
+        <v>63.4</v>
       </c>
       <c r="D2" t="n">
-        <v>60.13</v>
+        <v>63.27</v>
       </c>
       <c r="E2" t="n">
-        <v>58.03</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D3" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E3" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E5" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E6" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D7" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E7" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D8" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E8" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D9" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D10" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E10" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,40 +656,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D11" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D12" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E12" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E13" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D14" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E15" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D16" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E16" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E17" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D18" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E18" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D19" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D20" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D21" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D22" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E22" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D23" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E23" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E24" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D25" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D25" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E25" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D26" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E26" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D27" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E28" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1034,33 +1034,12 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D29" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E29" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D30" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E30" t="n">
         <v>54.08</v>
       </c>
     </row>

--- a/IC期货基差数据_最终版.xlsx
+++ b/IC期货基差数据_最终版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>63.4</v>
+        <v>58.4</v>
       </c>
       <c r="D2" t="n">
-        <v>63.27</v>
+        <v>59.87</v>
       </c>
       <c r="E2" t="n">
-        <v>60.3</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>58.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>59.87</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>57.03</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="E4" t="n">
-        <v>61.67</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>64.2</v>
+        <v>63.27</v>
       </c>
       <c r="E5" t="n">
-        <v>62.37</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D6" t="n">
-        <v>63.27</v>
+        <v>63.2</v>
       </c>
       <c r="E6" t="n">
-        <v>61.77</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D7" t="n">
-        <v>63.2</v>
+        <v>59.4</v>
       </c>
       <c r="E7" t="n">
-        <v>61.37</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>66.2</v>
+        <v>75</v>
       </c>
       <c r="D8" t="n">
-        <v>59.4</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>59.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>67.8</v>
       </c>
       <c r="D9" t="n">
-        <v>65.93000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E9" t="n">
-        <v>62.97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,40 +635,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="D10" t="n">
-        <v>61.4</v>
+        <v>55.13</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IC2606</t>
+          <t>IC2607</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="D11" t="n">
-        <v>55.13</v>
+        <v>68.5</v>
       </c>
       <c r="E11" t="n">
-        <v>56.9</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>61.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="E12" t="n">
-        <v>64.28</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="D13" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>64.95999999999999</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,19 +719,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>71.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E14" t="n">
-        <v>67.28</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>89.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D15" t="n">
-        <v>84.3</v>
+        <v>88.8</v>
       </c>
       <c r="E15" t="n">
-        <v>74.16</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>93.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>88.8</v>
+        <v>82.2</v>
       </c>
       <c r="E16" t="n">
-        <v>78.04000000000001</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="E17" t="n">
-        <v>76.76000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D18" t="n">
-        <v>87</v>
+        <v>75.5</v>
       </c>
       <c r="E18" t="n">
-        <v>79</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>82</v>
+        <v>80.8</v>
       </c>
       <c r="D19" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>71.40000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>80.8</v>
+        <v>86.8</v>
       </c>
       <c r="D20" t="n">
-        <v>75.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>70.84</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>86.8</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E21" t="n">
-        <v>72.36</v>
+        <v>71.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D22" t="n">
-        <v>75.3</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
-        <v>71.44</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>59.6</v>
       </c>
       <c r="E23" t="n">
-        <v>64.36</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D24" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D24" t="n">
-        <v>59.6</v>
-      </c>
       <c r="E24" t="n">
-        <v>60.52</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>80.2</v>
+        <v>62.8</v>
       </c>
       <c r="D25" t="n">
-        <v>68.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E25" t="n">
-        <v>65.04000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>62.8</v>
+        <v>69.2</v>
       </c>
       <c r="D26" t="n">
-        <v>58.6</v>
+        <v>62.5</v>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>69.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>62.5</v>
+        <v>57.3</v>
       </c>
       <c r="E27" t="n">
-        <v>61.88</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1013,33 +1013,12 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>64.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="D28" t="n">
-        <v>57.3</v>
+        <v>47.3</v>
       </c>
       <c r="E28" t="n">
-        <v>60.16</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>IC2607</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="D29" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E29" t="n">
         <v>54.08</v>
       </c>
     </row>
